--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>DAY</t>
   </si>
@@ -680,8 +680,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sp.: Data security management - Lecture 20h
-Rafał Stęgierski, PhD
+      <t xml:space="preserve">Numerical Methods - Lecture 20h
+Tomasz Giżewski, PhD
 dates: 07.10, 14.10, 21.10, 28.10, 04.11, 18.11, 25.11, 02.12, 09.12, 16.12
 </t>
     </r>
@@ -695,182 +695,6 @@
         <charset val="238"/>
       </rPr>
       <t>on-line classes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Security of IT systems - Lecture 20h
-Karol Kuczyński, PhD
-dates: 07.10, 14.10, 21.10, 28.10, 04.11, 18.11, 25.11, 02.12, 09.12, 16.12
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>on-line classes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sp.: IT security audit - Lecture 20h
-Emil Tomczyk, MA
-dates: 07.10, 14.10, 21.10, 28.10, 04.11, 18.11, 25.11, 02.12, 09.12, 16.12
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>on-line classes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sp.: Internet of things - Lecture 20h
-Róża Dzierżak, PhD
-dates: 08.10, 15.10, 22.10, 29.10, 05.11, 12.11, 19.11, 26.11, 03.12, 10.12
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>on-line classes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Numerical Methods - Lecture 20h
-Tomasz Giżewski, PhD
-dates: 08.10, 15.10, 22.10, 29.10, 05.11, 12.11, 19.11, 26.11, 03.12, 10.12
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>on-line classes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Numerical Methods - Lab 30h
-Tomasz Giżewski, PhD
-dates: 09.10, 16.10, 23.10, 30.10, 06.11, 13.11, 20.11, 27.11, 04.12, 11.12
-room
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>classes at the seat of the University</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sp.: Internet of things - Lab 30h
-Róża Dzierżak, PhD
-dates: 11.10, 18.10, 25.10, 08.11, 15.11, 22.11, 29.11, 06.12, 13.12, 20.12
-room
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>classes at the seat of the University</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sp.: IT security audit - Lab 30h
-Emil Tomczyk, MA
-dates: 11.10, 18.10, 25.10, 08.11, 15.11, 22.11, 29.11, 06.12, 13.12, 20.12
-room
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>classes at the seat of the University</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Data security management - Lab 40h
-Rafał Stęgierski, PhD
-dates: 17.10, 24.10, 31.10, 07.11, 14.11, 21.11, 28.11, 05.12, 12.12, 19.12
-room
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>classes at the seat of the University</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Management of information technology projects - Project 20h
-Rafał Stęgierski, PhD
-dates: 17.10, 24.10, 31.10, 07.11, 14.11, 21.11, 28.11, 05.12, 12.12, 19.12
-room
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>classes at the seat of the University</t>
     </r>
   </si>
   <si>
@@ -878,6 +702,176 @@
       <t xml:space="preserve">Awareness of values -Workshop 15h
 Marcin Garbowski, PhD
 dates: 08.10, 15.10, 22.10, 05.11, 12.11
+room 221
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>classes at the seat of the University</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Numerical Methods - Lab 30h
+Tomasz Giżewski, PhD
+dates: 15.10, 22.10, 29.10, 05.11, 12.11, 19.11, 26.11, 03.12, 10.12, 17.12
+room 205
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>classes at the seat of the University</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A group project of an information system - Project 40h
+Monika Kaczorowska, PhD
+dates: 16.10, 23.10, 20.11, 04.12, 11.12, 15.01, 22.01, 29.01
+room 205
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>classes at the seat of the University</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Security of IT systems - Lecture 20h
+Karol Kuczyński, PhD
+dates: 07.10, 21.10, 28.10, 04.11, 18.11, 25.11, 02.12, 09.12, 16.12, 13.01
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sp.: Data security management - Lecture 20h
+dates: 18.11, 25.11, 02.12, 09.12, 16.12
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sp.: Internet of things - Lecture 20h
+dates: 26.11, 03.12, 10.12, 17.12, 12.01, 19.01, 26.01
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sp.: IT security audit - Lecture 20h
+dates:  25.11, 02.12, 09.12, 16.12, 13.01, 20.01, 27.01
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A group project of an information system - Lecture
+Monika Kaczorowska, PhD
+dates: 27.11
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A group project of an information system - Lecture 20h
+Monika Kaczorowska, PhD
+dates: 07.10, 14.10, 21.10, 18.11, 02.12, 09.12, 16.12, 20.01, 27.01
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>on-line classes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Data security management - Lab 40h
+dates: 14.11, 21.11, 28.11, 05.12, 12.12, 19.12, 09.01, 16.01, 23.01, 30.01
 room
 </t>
     </r>
@@ -895,9 +889,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">A group project of an information system - Project 40h
-Monika Kaczorowska, PhD
-dates: 09.10, 16.10, 23.10, 30.10,, 13.11, 20.11, 27.11, 04.12
+      <t xml:space="preserve">Sp.: Internet of things - Lab 30h
+dates: 15.11, 22.11, 29.11, 06.12, 13.12, 20.12, 10.01, 17.01, 24.01, 31.01
 room
 </t>
     </r>
@@ -915,9 +908,9 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">A group project of an information system - Lecture 20h
-Monika Kaczorowska, PhD
-dates: 07.10, 14.10, 21.10, 28.10, 18.11, 25.11, 02.12, 09.12, 16.12, 13.01
+      <t xml:space="preserve">Sp.: IT security audit - Lab 30h
+dates: 15.11, 22.11, 29.11, 06.12, 13.12, 20.12, 10.01, 17.01, 24.01, 31.01
+room
 </t>
     </r>
     <r>
@@ -929,7 +922,28 @@
         <family val="1"/>
         <charset val="238"/>
       </rPr>
-      <t>on-line classes</t>
+      <t>classes at the seat of the University</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Management of information technology projects - Project 20h
+Rafał Stęgierski, PhD
+dates: 17.10, 24.10, 31.10, 07.11, 14.11, 21.11, 28.11
+on 14.11, 21.11, 28.11 classes at 13:30-16:50
+room 211
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>classes at the seat of the University</t>
     </r>
   </si>
 </sst>
@@ -1271,17 +1285,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -1323,36 +1326,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1517,11 +1490,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1550,98 +1562,101 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1927,853 +1942,853 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2" max="6" width="42.7109375" style="1" customWidth="1"/>
-    <col min="7" max="227" width="9.140625" style="1"/>
-    <col min="228" max="228" width="13.28515625" style="1" customWidth="1"/>
-    <col min="229" max="229" width="32.28515625" style="1" customWidth="1"/>
-    <col min="230" max="230" width="31.85546875" style="1" customWidth="1"/>
-    <col min="231" max="231" width="32.28515625" style="1" customWidth="1"/>
-    <col min="232" max="232" width="31.85546875" style="1" customWidth="1"/>
-    <col min="233" max="234" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2" max="6" width="42.7265625" style="1" customWidth="1"/>
+    <col min="7" max="227" width="9.1796875" style="1"/>
+    <col min="228" max="228" width="13.26953125" style="1" customWidth="1"/>
+    <col min="229" max="229" width="32.26953125" style="1" customWidth="1"/>
+    <col min="230" max="230" width="31.81640625" style="1" customWidth="1"/>
+    <col min="231" max="231" width="32.26953125" style="1" customWidth="1"/>
+    <col min="232" max="232" width="31.81640625" style="1" customWidth="1"/>
+    <col min="233" max="234" width="28.7265625" style="1" customWidth="1"/>
     <col min="235" max="235" width="29" style="1" customWidth="1"/>
-    <col min="236" max="236" width="29.28515625" style="1" customWidth="1"/>
-    <col min="237" max="238" width="28.7109375" style="1" customWidth="1"/>
-    <col min="239" max="241" width="9.140625" style="1"/>
-    <col min="242" max="242" width="36.85546875" style="1" customWidth="1"/>
-    <col min="243" max="243" width="31.28515625" style="1" customWidth="1"/>
-    <col min="244" max="483" width="9.140625" style="1"/>
-    <col min="484" max="484" width="13.28515625" style="1" customWidth="1"/>
-    <col min="485" max="485" width="32.28515625" style="1" customWidth="1"/>
-    <col min="486" max="486" width="31.85546875" style="1" customWidth="1"/>
-    <col min="487" max="487" width="32.28515625" style="1" customWidth="1"/>
-    <col min="488" max="488" width="31.85546875" style="1" customWidth="1"/>
-    <col min="489" max="490" width="28.7109375" style="1" customWidth="1"/>
+    <col min="236" max="236" width="29.26953125" style="1" customWidth="1"/>
+    <col min="237" max="238" width="28.7265625" style="1" customWidth="1"/>
+    <col min="239" max="241" width="9.1796875" style="1"/>
+    <col min="242" max="242" width="36.81640625" style="1" customWidth="1"/>
+    <col min="243" max="243" width="31.26953125" style="1" customWidth="1"/>
+    <col min="244" max="483" width="9.1796875" style="1"/>
+    <col min="484" max="484" width="13.26953125" style="1" customWidth="1"/>
+    <col min="485" max="485" width="32.26953125" style="1" customWidth="1"/>
+    <col min="486" max="486" width="31.81640625" style="1" customWidth="1"/>
+    <col min="487" max="487" width="32.26953125" style="1" customWidth="1"/>
+    <col min="488" max="488" width="31.81640625" style="1" customWidth="1"/>
+    <col min="489" max="490" width="28.7265625" style="1" customWidth="1"/>
     <col min="491" max="491" width="29" style="1" customWidth="1"/>
-    <col min="492" max="492" width="29.28515625" style="1" customWidth="1"/>
-    <col min="493" max="494" width="28.7109375" style="1" customWidth="1"/>
-    <col min="495" max="497" width="9.140625" style="1"/>
-    <col min="498" max="498" width="36.85546875" style="1" customWidth="1"/>
-    <col min="499" max="499" width="31.28515625" style="1" customWidth="1"/>
-    <col min="500" max="739" width="9.140625" style="1"/>
-    <col min="740" max="740" width="13.28515625" style="1" customWidth="1"/>
-    <col min="741" max="741" width="32.28515625" style="1" customWidth="1"/>
-    <col min="742" max="742" width="31.85546875" style="1" customWidth="1"/>
-    <col min="743" max="743" width="32.28515625" style="1" customWidth="1"/>
-    <col min="744" max="744" width="31.85546875" style="1" customWidth="1"/>
-    <col min="745" max="746" width="28.7109375" style="1" customWidth="1"/>
+    <col min="492" max="492" width="29.26953125" style="1" customWidth="1"/>
+    <col min="493" max="494" width="28.7265625" style="1" customWidth="1"/>
+    <col min="495" max="497" width="9.1796875" style="1"/>
+    <col min="498" max="498" width="36.81640625" style="1" customWidth="1"/>
+    <col min="499" max="499" width="31.26953125" style="1" customWidth="1"/>
+    <col min="500" max="739" width="9.1796875" style="1"/>
+    <col min="740" max="740" width="13.26953125" style="1" customWidth="1"/>
+    <col min="741" max="741" width="32.26953125" style="1" customWidth="1"/>
+    <col min="742" max="742" width="31.81640625" style="1" customWidth="1"/>
+    <col min="743" max="743" width="32.26953125" style="1" customWidth="1"/>
+    <col min="744" max="744" width="31.81640625" style="1" customWidth="1"/>
+    <col min="745" max="746" width="28.7265625" style="1" customWidth="1"/>
     <col min="747" max="747" width="29" style="1" customWidth="1"/>
-    <col min="748" max="748" width="29.28515625" style="1" customWidth="1"/>
-    <col min="749" max="750" width="28.7109375" style="1" customWidth="1"/>
-    <col min="751" max="753" width="9.140625" style="1"/>
-    <col min="754" max="754" width="36.85546875" style="1" customWidth="1"/>
-    <col min="755" max="755" width="31.28515625" style="1" customWidth="1"/>
-    <col min="756" max="995" width="9.140625" style="1"/>
-    <col min="996" max="996" width="13.28515625" style="1" customWidth="1"/>
-    <col min="997" max="997" width="32.28515625" style="1" customWidth="1"/>
-    <col min="998" max="998" width="31.85546875" style="1" customWidth="1"/>
-    <col min="999" max="999" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1000" max="1000" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1001" max="1002" width="28.7109375" style="1" customWidth="1"/>
+    <col min="748" max="748" width="29.26953125" style="1" customWidth="1"/>
+    <col min="749" max="750" width="28.7265625" style="1" customWidth="1"/>
+    <col min="751" max="753" width="9.1796875" style="1"/>
+    <col min="754" max="754" width="36.81640625" style="1" customWidth="1"/>
+    <col min="755" max="755" width="31.26953125" style="1" customWidth="1"/>
+    <col min="756" max="995" width="9.1796875" style="1"/>
+    <col min="996" max="996" width="13.26953125" style="1" customWidth="1"/>
+    <col min="997" max="997" width="32.26953125" style="1" customWidth="1"/>
+    <col min="998" max="998" width="31.81640625" style="1" customWidth="1"/>
+    <col min="999" max="999" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1000" max="1000" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1001" max="1002" width="28.7265625" style="1" customWidth="1"/>
     <col min="1003" max="1003" width="29" style="1" customWidth="1"/>
-    <col min="1004" max="1004" width="29.28515625" style="1" customWidth="1"/>
-    <col min="1005" max="1006" width="28.7109375" style="1" customWidth="1"/>
-    <col min="1007" max="1009" width="9.140625" style="1"/>
-    <col min="1010" max="1010" width="36.85546875" style="1" customWidth="1"/>
-    <col min="1011" max="1011" width="31.28515625" style="1" customWidth="1"/>
-    <col min="1012" max="1251" width="9.140625" style="1"/>
-    <col min="1252" max="1252" width="13.28515625" style="1" customWidth="1"/>
-    <col min="1253" max="1253" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1254" max="1254" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1255" max="1255" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1256" max="1256" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1257" max="1258" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1004" max="1004" width="29.26953125" style="1" customWidth="1"/>
+    <col min="1005" max="1006" width="28.7265625" style="1" customWidth="1"/>
+    <col min="1007" max="1009" width="9.1796875" style="1"/>
+    <col min="1010" max="1010" width="36.81640625" style="1" customWidth="1"/>
+    <col min="1011" max="1011" width="31.26953125" style="1" customWidth="1"/>
+    <col min="1012" max="1251" width="9.1796875" style="1"/>
+    <col min="1252" max="1252" width="13.26953125" style="1" customWidth="1"/>
+    <col min="1253" max="1253" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1254" max="1254" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1255" max="1255" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1256" max="1256" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1257" max="1258" width="28.7265625" style="1" customWidth="1"/>
     <col min="1259" max="1259" width="29" style="1" customWidth="1"/>
-    <col min="1260" max="1260" width="29.28515625" style="1" customWidth="1"/>
-    <col min="1261" max="1262" width="28.7109375" style="1" customWidth="1"/>
-    <col min="1263" max="1265" width="9.140625" style="1"/>
-    <col min="1266" max="1266" width="36.85546875" style="1" customWidth="1"/>
-    <col min="1267" max="1267" width="31.28515625" style="1" customWidth="1"/>
-    <col min="1268" max="1507" width="9.140625" style="1"/>
-    <col min="1508" max="1508" width="13.28515625" style="1" customWidth="1"/>
-    <col min="1509" max="1509" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1510" max="1510" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1511" max="1511" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1512" max="1512" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1513" max="1514" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1260" max="1260" width="29.26953125" style="1" customWidth="1"/>
+    <col min="1261" max="1262" width="28.7265625" style="1" customWidth="1"/>
+    <col min="1263" max="1265" width="9.1796875" style="1"/>
+    <col min="1266" max="1266" width="36.81640625" style="1" customWidth="1"/>
+    <col min="1267" max="1267" width="31.26953125" style="1" customWidth="1"/>
+    <col min="1268" max="1507" width="9.1796875" style="1"/>
+    <col min="1508" max="1508" width="13.26953125" style="1" customWidth="1"/>
+    <col min="1509" max="1509" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1510" max="1510" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1511" max="1511" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1512" max="1512" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1513" max="1514" width="28.7265625" style="1" customWidth="1"/>
     <col min="1515" max="1515" width="29" style="1" customWidth="1"/>
-    <col min="1516" max="1516" width="29.28515625" style="1" customWidth="1"/>
-    <col min="1517" max="1518" width="28.7109375" style="1" customWidth="1"/>
-    <col min="1519" max="1521" width="9.140625" style="1"/>
-    <col min="1522" max="1522" width="36.85546875" style="1" customWidth="1"/>
-    <col min="1523" max="1523" width="31.28515625" style="1" customWidth="1"/>
-    <col min="1524" max="1763" width="9.140625" style="1"/>
-    <col min="1764" max="1764" width="13.28515625" style="1" customWidth="1"/>
-    <col min="1765" max="1765" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1766" max="1766" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1767" max="1767" width="32.28515625" style="1" customWidth="1"/>
-    <col min="1768" max="1768" width="31.85546875" style="1" customWidth="1"/>
-    <col min="1769" max="1770" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1516" max="1516" width="29.26953125" style="1" customWidth="1"/>
+    <col min="1517" max="1518" width="28.7265625" style="1" customWidth="1"/>
+    <col min="1519" max="1521" width="9.1796875" style="1"/>
+    <col min="1522" max="1522" width="36.81640625" style="1" customWidth="1"/>
+    <col min="1523" max="1523" width="31.26953125" style="1" customWidth="1"/>
+    <col min="1524" max="1763" width="9.1796875" style="1"/>
+    <col min="1764" max="1764" width="13.26953125" style="1" customWidth="1"/>
+    <col min="1765" max="1765" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1766" max="1766" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1767" max="1767" width="32.26953125" style="1" customWidth="1"/>
+    <col min="1768" max="1768" width="31.81640625" style="1" customWidth="1"/>
+    <col min="1769" max="1770" width="28.7265625" style="1" customWidth="1"/>
     <col min="1771" max="1771" width="29" style="1" customWidth="1"/>
-    <col min="1772" max="1772" width="29.28515625" style="1" customWidth="1"/>
-    <col min="1773" max="1774" width="28.7109375" style="1" customWidth="1"/>
-    <col min="1775" max="1777" width="9.140625" style="1"/>
-    <col min="1778" max="1778" width="36.85546875" style="1" customWidth="1"/>
-    <col min="1779" max="1779" width="31.28515625" style="1" customWidth="1"/>
-    <col min="1780" max="2019" width="9.140625" style="1"/>
-    <col min="2020" max="2020" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2021" max="2021" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2022" max="2022" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2023" max="2023" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2024" max="2024" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2025" max="2026" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1772" max="1772" width="29.26953125" style="1" customWidth="1"/>
+    <col min="1773" max="1774" width="28.7265625" style="1" customWidth="1"/>
+    <col min="1775" max="1777" width="9.1796875" style="1"/>
+    <col min="1778" max="1778" width="36.81640625" style="1" customWidth="1"/>
+    <col min="1779" max="1779" width="31.26953125" style="1" customWidth="1"/>
+    <col min="1780" max="2019" width="9.1796875" style="1"/>
+    <col min="2020" max="2020" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2021" max="2021" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2022" max="2022" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2023" max="2023" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2024" max="2024" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2025" max="2026" width="28.7265625" style="1" customWidth="1"/>
     <col min="2027" max="2027" width="29" style="1" customWidth="1"/>
-    <col min="2028" max="2028" width="29.28515625" style="1" customWidth="1"/>
-    <col min="2029" max="2030" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2031" max="2033" width="9.140625" style="1"/>
-    <col min="2034" max="2034" width="36.85546875" style="1" customWidth="1"/>
-    <col min="2035" max="2035" width="31.28515625" style="1" customWidth="1"/>
-    <col min="2036" max="2275" width="9.140625" style="1"/>
-    <col min="2276" max="2276" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2277" max="2277" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2278" max="2278" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2279" max="2279" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2280" max="2280" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2281" max="2282" width="28.7109375" style="1" customWidth="1"/>
+    <col min="2028" max="2028" width="29.26953125" style="1" customWidth="1"/>
+    <col min="2029" max="2030" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2031" max="2033" width="9.1796875" style="1"/>
+    <col min="2034" max="2034" width="36.81640625" style="1" customWidth="1"/>
+    <col min="2035" max="2035" width="31.26953125" style="1" customWidth="1"/>
+    <col min="2036" max="2275" width="9.1796875" style="1"/>
+    <col min="2276" max="2276" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2277" max="2277" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2278" max="2278" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2279" max="2279" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2280" max="2280" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2281" max="2282" width="28.7265625" style="1" customWidth="1"/>
     <col min="2283" max="2283" width="29" style="1" customWidth="1"/>
-    <col min="2284" max="2284" width="29.28515625" style="1" customWidth="1"/>
-    <col min="2285" max="2286" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2287" max="2289" width="9.140625" style="1"/>
-    <col min="2290" max="2290" width="36.85546875" style="1" customWidth="1"/>
-    <col min="2291" max="2291" width="31.28515625" style="1" customWidth="1"/>
-    <col min="2292" max="2531" width="9.140625" style="1"/>
-    <col min="2532" max="2532" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2533" max="2533" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2534" max="2534" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2535" max="2535" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2536" max="2536" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2537" max="2538" width="28.7109375" style="1" customWidth="1"/>
+    <col min="2284" max="2284" width="29.26953125" style="1" customWidth="1"/>
+    <col min="2285" max="2286" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2287" max="2289" width="9.1796875" style="1"/>
+    <col min="2290" max="2290" width="36.81640625" style="1" customWidth="1"/>
+    <col min="2291" max="2291" width="31.26953125" style="1" customWidth="1"/>
+    <col min="2292" max="2531" width="9.1796875" style="1"/>
+    <col min="2532" max="2532" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2533" max="2533" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2534" max="2534" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2535" max="2535" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2536" max="2536" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2537" max="2538" width="28.7265625" style="1" customWidth="1"/>
     <col min="2539" max="2539" width="29" style="1" customWidth="1"/>
-    <col min="2540" max="2540" width="29.28515625" style="1" customWidth="1"/>
-    <col min="2541" max="2542" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2543" max="2545" width="9.140625" style="1"/>
-    <col min="2546" max="2546" width="36.85546875" style="1" customWidth="1"/>
-    <col min="2547" max="2547" width="31.28515625" style="1" customWidth="1"/>
-    <col min="2548" max="2787" width="9.140625" style="1"/>
-    <col min="2788" max="2788" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2789" max="2789" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2790" max="2790" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2791" max="2791" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2792" max="2792" width="31.85546875" style="1" customWidth="1"/>
-    <col min="2793" max="2794" width="28.7109375" style="1" customWidth="1"/>
+    <col min="2540" max="2540" width="29.26953125" style="1" customWidth="1"/>
+    <col min="2541" max="2542" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2543" max="2545" width="9.1796875" style="1"/>
+    <col min="2546" max="2546" width="36.81640625" style="1" customWidth="1"/>
+    <col min="2547" max="2547" width="31.26953125" style="1" customWidth="1"/>
+    <col min="2548" max="2787" width="9.1796875" style="1"/>
+    <col min="2788" max="2788" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2789" max="2789" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2790" max="2790" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2791" max="2791" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2792" max="2792" width="31.81640625" style="1" customWidth="1"/>
+    <col min="2793" max="2794" width="28.7265625" style="1" customWidth="1"/>
     <col min="2795" max="2795" width="29" style="1" customWidth="1"/>
-    <col min="2796" max="2796" width="29.28515625" style="1" customWidth="1"/>
-    <col min="2797" max="2798" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2799" max="2801" width="9.140625" style="1"/>
-    <col min="2802" max="2802" width="36.85546875" style="1" customWidth="1"/>
-    <col min="2803" max="2803" width="31.28515625" style="1" customWidth="1"/>
-    <col min="2804" max="3043" width="9.140625" style="1"/>
-    <col min="3044" max="3044" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3045" max="3045" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3046" max="3046" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3047" max="3047" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3048" max="3048" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3049" max="3050" width="28.7109375" style="1" customWidth="1"/>
+    <col min="2796" max="2796" width="29.26953125" style="1" customWidth="1"/>
+    <col min="2797" max="2798" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2799" max="2801" width="9.1796875" style="1"/>
+    <col min="2802" max="2802" width="36.81640625" style="1" customWidth="1"/>
+    <col min="2803" max="2803" width="31.26953125" style="1" customWidth="1"/>
+    <col min="2804" max="3043" width="9.1796875" style="1"/>
+    <col min="3044" max="3044" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3045" max="3045" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3046" max="3046" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3047" max="3047" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3048" max="3048" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3049" max="3050" width="28.7265625" style="1" customWidth="1"/>
     <col min="3051" max="3051" width="29" style="1" customWidth="1"/>
-    <col min="3052" max="3052" width="29.28515625" style="1" customWidth="1"/>
-    <col min="3053" max="3054" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3055" max="3057" width="9.140625" style="1"/>
-    <col min="3058" max="3058" width="36.85546875" style="1" customWidth="1"/>
-    <col min="3059" max="3059" width="31.28515625" style="1" customWidth="1"/>
-    <col min="3060" max="3299" width="9.140625" style="1"/>
-    <col min="3300" max="3300" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3301" max="3301" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3302" max="3302" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3303" max="3303" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3304" max="3304" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3305" max="3306" width="28.7109375" style="1" customWidth="1"/>
+    <col min="3052" max="3052" width="29.26953125" style="1" customWidth="1"/>
+    <col min="3053" max="3054" width="28.7265625" style="1" customWidth="1"/>
+    <col min="3055" max="3057" width="9.1796875" style="1"/>
+    <col min="3058" max="3058" width="36.81640625" style="1" customWidth="1"/>
+    <col min="3059" max="3059" width="31.26953125" style="1" customWidth="1"/>
+    <col min="3060" max="3299" width="9.1796875" style="1"/>
+    <col min="3300" max="3300" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3301" max="3301" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3302" max="3302" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3303" max="3303" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3304" max="3304" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3305" max="3306" width="28.7265625" style="1" customWidth="1"/>
     <col min="3307" max="3307" width="29" style="1" customWidth="1"/>
-    <col min="3308" max="3308" width="29.28515625" style="1" customWidth="1"/>
-    <col min="3309" max="3310" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3311" max="3313" width="9.140625" style="1"/>
-    <col min="3314" max="3314" width="36.85546875" style="1" customWidth="1"/>
-    <col min="3315" max="3315" width="31.28515625" style="1" customWidth="1"/>
-    <col min="3316" max="3555" width="9.140625" style="1"/>
-    <col min="3556" max="3556" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3557" max="3557" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3558" max="3558" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3559" max="3559" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3560" max="3560" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3561" max="3562" width="28.7109375" style="1" customWidth="1"/>
+    <col min="3308" max="3308" width="29.26953125" style="1" customWidth="1"/>
+    <col min="3309" max="3310" width="28.7265625" style="1" customWidth="1"/>
+    <col min="3311" max="3313" width="9.1796875" style="1"/>
+    <col min="3314" max="3314" width="36.81640625" style="1" customWidth="1"/>
+    <col min="3315" max="3315" width="31.26953125" style="1" customWidth="1"/>
+    <col min="3316" max="3555" width="9.1796875" style="1"/>
+    <col min="3556" max="3556" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3557" max="3557" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3558" max="3558" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3559" max="3559" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3560" max="3560" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3561" max="3562" width="28.7265625" style="1" customWidth="1"/>
     <col min="3563" max="3563" width="29" style="1" customWidth="1"/>
-    <col min="3564" max="3564" width="29.28515625" style="1" customWidth="1"/>
-    <col min="3565" max="3566" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3567" max="3569" width="9.140625" style="1"/>
-    <col min="3570" max="3570" width="36.85546875" style="1" customWidth="1"/>
-    <col min="3571" max="3571" width="31.28515625" style="1" customWidth="1"/>
-    <col min="3572" max="3811" width="9.140625" style="1"/>
-    <col min="3812" max="3812" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3813" max="3813" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3814" max="3814" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3815" max="3815" width="32.28515625" style="1" customWidth="1"/>
-    <col min="3816" max="3816" width="31.85546875" style="1" customWidth="1"/>
-    <col min="3817" max="3818" width="28.7109375" style="1" customWidth="1"/>
+    <col min="3564" max="3564" width="29.26953125" style="1" customWidth="1"/>
+    <col min="3565" max="3566" width="28.7265625" style="1" customWidth="1"/>
+    <col min="3567" max="3569" width="9.1796875" style="1"/>
+    <col min="3570" max="3570" width="36.81640625" style="1" customWidth="1"/>
+    <col min="3571" max="3571" width="31.26953125" style="1" customWidth="1"/>
+    <col min="3572" max="3811" width="9.1796875" style="1"/>
+    <col min="3812" max="3812" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3813" max="3813" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3814" max="3814" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3815" max="3815" width="32.26953125" style="1" customWidth="1"/>
+    <col min="3816" max="3816" width="31.81640625" style="1" customWidth="1"/>
+    <col min="3817" max="3818" width="28.7265625" style="1" customWidth="1"/>
     <col min="3819" max="3819" width="29" style="1" customWidth="1"/>
-    <col min="3820" max="3820" width="29.28515625" style="1" customWidth="1"/>
-    <col min="3821" max="3822" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3823" max="3825" width="9.140625" style="1"/>
-    <col min="3826" max="3826" width="36.85546875" style="1" customWidth="1"/>
-    <col min="3827" max="3827" width="31.28515625" style="1" customWidth="1"/>
-    <col min="3828" max="4067" width="9.140625" style="1"/>
-    <col min="4068" max="4068" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4069" max="4069" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4070" max="4070" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4071" max="4071" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4072" max="4072" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4073" max="4074" width="28.7109375" style="1" customWidth="1"/>
+    <col min="3820" max="3820" width="29.26953125" style="1" customWidth="1"/>
+    <col min="3821" max="3822" width="28.7265625" style="1" customWidth="1"/>
+    <col min="3823" max="3825" width="9.1796875" style="1"/>
+    <col min="3826" max="3826" width="36.81640625" style="1" customWidth="1"/>
+    <col min="3827" max="3827" width="31.26953125" style="1" customWidth="1"/>
+    <col min="3828" max="4067" width="9.1796875" style="1"/>
+    <col min="4068" max="4068" width="13.26953125" style="1" customWidth="1"/>
+    <col min="4069" max="4069" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4070" max="4070" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4071" max="4071" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4072" max="4072" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4073" max="4074" width="28.7265625" style="1" customWidth="1"/>
     <col min="4075" max="4075" width="29" style="1" customWidth="1"/>
-    <col min="4076" max="4076" width="29.28515625" style="1" customWidth="1"/>
-    <col min="4077" max="4078" width="28.7109375" style="1" customWidth="1"/>
-    <col min="4079" max="4081" width="9.140625" style="1"/>
-    <col min="4082" max="4082" width="36.85546875" style="1" customWidth="1"/>
-    <col min="4083" max="4083" width="31.28515625" style="1" customWidth="1"/>
-    <col min="4084" max="4323" width="9.140625" style="1"/>
-    <col min="4324" max="4324" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4325" max="4325" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4326" max="4326" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4327" max="4327" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4328" max="4328" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4329" max="4330" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4076" max="4076" width="29.26953125" style="1" customWidth="1"/>
+    <col min="4077" max="4078" width="28.7265625" style="1" customWidth="1"/>
+    <col min="4079" max="4081" width="9.1796875" style="1"/>
+    <col min="4082" max="4082" width="36.81640625" style="1" customWidth="1"/>
+    <col min="4083" max="4083" width="31.26953125" style="1" customWidth="1"/>
+    <col min="4084" max="4323" width="9.1796875" style="1"/>
+    <col min="4324" max="4324" width="13.26953125" style="1" customWidth="1"/>
+    <col min="4325" max="4325" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4326" max="4326" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4327" max="4327" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4328" max="4328" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4329" max="4330" width="28.7265625" style="1" customWidth="1"/>
     <col min="4331" max="4331" width="29" style="1" customWidth="1"/>
-    <col min="4332" max="4332" width="29.28515625" style="1" customWidth="1"/>
-    <col min="4333" max="4334" width="28.7109375" style="1" customWidth="1"/>
-    <col min="4335" max="4337" width="9.140625" style="1"/>
-    <col min="4338" max="4338" width="36.85546875" style="1" customWidth="1"/>
-    <col min="4339" max="4339" width="31.28515625" style="1" customWidth="1"/>
-    <col min="4340" max="4579" width="9.140625" style="1"/>
-    <col min="4580" max="4580" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4581" max="4581" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4582" max="4582" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4583" max="4583" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4584" max="4584" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4585" max="4586" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4332" max="4332" width="29.26953125" style="1" customWidth="1"/>
+    <col min="4333" max="4334" width="28.7265625" style="1" customWidth="1"/>
+    <col min="4335" max="4337" width="9.1796875" style="1"/>
+    <col min="4338" max="4338" width="36.81640625" style="1" customWidth="1"/>
+    <col min="4339" max="4339" width="31.26953125" style="1" customWidth="1"/>
+    <col min="4340" max="4579" width="9.1796875" style="1"/>
+    <col min="4580" max="4580" width="13.26953125" style="1" customWidth="1"/>
+    <col min="4581" max="4581" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4582" max="4582" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4583" max="4583" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4584" max="4584" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4585" max="4586" width="28.7265625" style="1" customWidth="1"/>
     <col min="4587" max="4587" width="29" style="1" customWidth="1"/>
-    <col min="4588" max="4588" width="29.28515625" style="1" customWidth="1"/>
-    <col min="4589" max="4590" width="28.7109375" style="1" customWidth="1"/>
-    <col min="4591" max="4593" width="9.140625" style="1"/>
-    <col min="4594" max="4594" width="36.85546875" style="1" customWidth="1"/>
-    <col min="4595" max="4595" width="31.28515625" style="1" customWidth="1"/>
-    <col min="4596" max="4835" width="9.140625" style="1"/>
-    <col min="4836" max="4836" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4837" max="4837" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4838" max="4838" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4839" max="4839" width="32.28515625" style="1" customWidth="1"/>
-    <col min="4840" max="4840" width="31.85546875" style="1" customWidth="1"/>
-    <col min="4841" max="4842" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4588" max="4588" width="29.26953125" style="1" customWidth="1"/>
+    <col min="4589" max="4590" width="28.7265625" style="1" customWidth="1"/>
+    <col min="4591" max="4593" width="9.1796875" style="1"/>
+    <col min="4594" max="4594" width="36.81640625" style="1" customWidth="1"/>
+    <col min="4595" max="4595" width="31.26953125" style="1" customWidth="1"/>
+    <col min="4596" max="4835" width="9.1796875" style="1"/>
+    <col min="4836" max="4836" width="13.26953125" style="1" customWidth="1"/>
+    <col min="4837" max="4837" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4838" max="4838" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4839" max="4839" width="32.26953125" style="1" customWidth="1"/>
+    <col min="4840" max="4840" width="31.81640625" style="1" customWidth="1"/>
+    <col min="4841" max="4842" width="28.7265625" style="1" customWidth="1"/>
     <col min="4843" max="4843" width="29" style="1" customWidth="1"/>
-    <col min="4844" max="4844" width="29.28515625" style="1" customWidth="1"/>
-    <col min="4845" max="4846" width="28.7109375" style="1" customWidth="1"/>
-    <col min="4847" max="4849" width="9.140625" style="1"/>
-    <col min="4850" max="4850" width="36.85546875" style="1" customWidth="1"/>
-    <col min="4851" max="4851" width="31.28515625" style="1" customWidth="1"/>
-    <col min="4852" max="5091" width="9.140625" style="1"/>
-    <col min="5092" max="5092" width="13.28515625" style="1" customWidth="1"/>
-    <col min="5093" max="5093" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5094" max="5094" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5095" max="5095" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5096" max="5096" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5097" max="5098" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4844" max="4844" width="29.26953125" style="1" customWidth="1"/>
+    <col min="4845" max="4846" width="28.7265625" style="1" customWidth="1"/>
+    <col min="4847" max="4849" width="9.1796875" style="1"/>
+    <col min="4850" max="4850" width="36.81640625" style="1" customWidth="1"/>
+    <col min="4851" max="4851" width="31.26953125" style="1" customWidth="1"/>
+    <col min="4852" max="5091" width="9.1796875" style="1"/>
+    <col min="5092" max="5092" width="13.26953125" style="1" customWidth="1"/>
+    <col min="5093" max="5093" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5094" max="5094" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5095" max="5095" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5096" max="5096" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5097" max="5098" width="28.7265625" style="1" customWidth="1"/>
     <col min="5099" max="5099" width="29" style="1" customWidth="1"/>
-    <col min="5100" max="5100" width="29.28515625" style="1" customWidth="1"/>
-    <col min="5101" max="5102" width="28.7109375" style="1" customWidth="1"/>
-    <col min="5103" max="5105" width="9.140625" style="1"/>
-    <col min="5106" max="5106" width="36.85546875" style="1" customWidth="1"/>
-    <col min="5107" max="5107" width="31.28515625" style="1" customWidth="1"/>
-    <col min="5108" max="5347" width="9.140625" style="1"/>
-    <col min="5348" max="5348" width="13.28515625" style="1" customWidth="1"/>
-    <col min="5349" max="5349" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5350" max="5350" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5351" max="5351" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5352" max="5352" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5353" max="5354" width="28.7109375" style="1" customWidth="1"/>
+    <col min="5100" max="5100" width="29.26953125" style="1" customWidth="1"/>
+    <col min="5101" max="5102" width="28.7265625" style="1" customWidth="1"/>
+    <col min="5103" max="5105" width="9.1796875" style="1"/>
+    <col min="5106" max="5106" width="36.81640625" style="1" customWidth="1"/>
+    <col min="5107" max="5107" width="31.26953125" style="1" customWidth="1"/>
+    <col min="5108" max="5347" width="9.1796875" style="1"/>
+    <col min="5348" max="5348" width="13.26953125" style="1" customWidth="1"/>
+    <col min="5349" max="5349" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5350" max="5350" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5351" max="5351" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5352" max="5352" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5353" max="5354" width="28.7265625" style="1" customWidth="1"/>
     <col min="5355" max="5355" width="29" style="1" customWidth="1"/>
-    <col min="5356" max="5356" width="29.28515625" style="1" customWidth="1"/>
-    <col min="5357" max="5358" width="28.7109375" style="1" customWidth="1"/>
-    <col min="5359" max="5361" width="9.140625" style="1"/>
-    <col min="5362" max="5362" width="36.85546875" style="1" customWidth="1"/>
-    <col min="5363" max="5363" width="31.28515625" style="1" customWidth="1"/>
-    <col min="5364" max="5603" width="9.140625" style="1"/>
-    <col min="5604" max="5604" width="13.28515625" style="1" customWidth="1"/>
-    <col min="5605" max="5605" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5606" max="5606" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5607" max="5607" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5608" max="5608" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5609" max="5610" width="28.7109375" style="1" customWidth="1"/>
+    <col min="5356" max="5356" width="29.26953125" style="1" customWidth="1"/>
+    <col min="5357" max="5358" width="28.7265625" style="1" customWidth="1"/>
+    <col min="5359" max="5361" width="9.1796875" style="1"/>
+    <col min="5362" max="5362" width="36.81640625" style="1" customWidth="1"/>
+    <col min="5363" max="5363" width="31.26953125" style="1" customWidth="1"/>
+    <col min="5364" max="5603" width="9.1796875" style="1"/>
+    <col min="5604" max="5604" width="13.26953125" style="1" customWidth="1"/>
+    <col min="5605" max="5605" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5606" max="5606" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5607" max="5607" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5608" max="5608" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5609" max="5610" width="28.7265625" style="1" customWidth="1"/>
     <col min="5611" max="5611" width="29" style="1" customWidth="1"/>
-    <col min="5612" max="5612" width="29.28515625" style="1" customWidth="1"/>
-    <col min="5613" max="5614" width="28.7109375" style="1" customWidth="1"/>
-    <col min="5615" max="5617" width="9.140625" style="1"/>
-    <col min="5618" max="5618" width="36.85546875" style="1" customWidth="1"/>
-    <col min="5619" max="5619" width="31.28515625" style="1" customWidth="1"/>
-    <col min="5620" max="5859" width="9.140625" style="1"/>
-    <col min="5860" max="5860" width="13.28515625" style="1" customWidth="1"/>
-    <col min="5861" max="5861" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5862" max="5862" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5863" max="5863" width="32.28515625" style="1" customWidth="1"/>
-    <col min="5864" max="5864" width="31.85546875" style="1" customWidth="1"/>
-    <col min="5865" max="5866" width="28.7109375" style="1" customWidth="1"/>
+    <col min="5612" max="5612" width="29.26953125" style="1" customWidth="1"/>
+    <col min="5613" max="5614" width="28.7265625" style="1" customWidth="1"/>
+    <col min="5615" max="5617" width="9.1796875" style="1"/>
+    <col min="5618" max="5618" width="36.81640625" style="1" customWidth="1"/>
+    <col min="5619" max="5619" width="31.26953125" style="1" customWidth="1"/>
+    <col min="5620" max="5859" width="9.1796875" style="1"/>
+    <col min="5860" max="5860" width="13.26953125" style="1" customWidth="1"/>
+    <col min="5861" max="5861" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5862" max="5862" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5863" max="5863" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5864" max="5864" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5865" max="5866" width="28.7265625" style="1" customWidth="1"/>
     <col min="5867" max="5867" width="29" style="1" customWidth="1"/>
-    <col min="5868" max="5868" width="29.28515625" style="1" customWidth="1"/>
-    <col min="5869" max="5870" width="28.7109375" style="1" customWidth="1"/>
-    <col min="5871" max="5873" width="9.140625" style="1"/>
-    <col min="5874" max="5874" width="36.85546875" style="1" customWidth="1"/>
-    <col min="5875" max="5875" width="31.28515625" style="1" customWidth="1"/>
-    <col min="5876" max="6115" width="9.140625" style="1"/>
-    <col min="6116" max="6116" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6117" max="6117" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6118" max="6118" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6119" max="6119" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6120" max="6120" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6121" max="6122" width="28.7109375" style="1" customWidth="1"/>
+    <col min="5868" max="5868" width="29.26953125" style="1" customWidth="1"/>
+    <col min="5869" max="5870" width="28.7265625" style="1" customWidth="1"/>
+    <col min="5871" max="5873" width="9.1796875" style="1"/>
+    <col min="5874" max="5874" width="36.81640625" style="1" customWidth="1"/>
+    <col min="5875" max="5875" width="31.26953125" style="1" customWidth="1"/>
+    <col min="5876" max="6115" width="9.1796875" style="1"/>
+    <col min="6116" max="6116" width="13.26953125" style="1" customWidth="1"/>
+    <col min="6117" max="6117" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6118" max="6118" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6119" max="6119" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6120" max="6120" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6121" max="6122" width="28.7265625" style="1" customWidth="1"/>
     <col min="6123" max="6123" width="29" style="1" customWidth="1"/>
-    <col min="6124" max="6124" width="29.28515625" style="1" customWidth="1"/>
-    <col min="6125" max="6126" width="28.7109375" style="1" customWidth="1"/>
-    <col min="6127" max="6129" width="9.140625" style="1"/>
-    <col min="6130" max="6130" width="36.85546875" style="1" customWidth="1"/>
-    <col min="6131" max="6131" width="31.28515625" style="1" customWidth="1"/>
-    <col min="6132" max="6371" width="9.140625" style="1"/>
-    <col min="6372" max="6372" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6373" max="6373" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6374" max="6374" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6375" max="6375" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6376" max="6376" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6377" max="6378" width="28.7109375" style="1" customWidth="1"/>
+    <col min="6124" max="6124" width="29.26953125" style="1" customWidth="1"/>
+    <col min="6125" max="6126" width="28.7265625" style="1" customWidth="1"/>
+    <col min="6127" max="6129" width="9.1796875" style="1"/>
+    <col min="6130" max="6130" width="36.81640625" style="1" customWidth="1"/>
+    <col min="6131" max="6131" width="31.26953125" style="1" customWidth="1"/>
+    <col min="6132" max="6371" width="9.1796875" style="1"/>
+    <col min="6372" max="6372" width="13.26953125" style="1" customWidth="1"/>
+    <col min="6373" max="6373" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6374" max="6374" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6375" max="6375" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6376" max="6376" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6377" max="6378" width="28.7265625" style="1" customWidth="1"/>
     <col min="6379" max="6379" width="29" style="1" customWidth="1"/>
-    <col min="6380" max="6380" width="29.28515625" style="1" customWidth="1"/>
-    <col min="6381" max="6382" width="28.7109375" style="1" customWidth="1"/>
-    <col min="6383" max="6385" width="9.140625" style="1"/>
-    <col min="6386" max="6386" width="36.85546875" style="1" customWidth="1"/>
-    <col min="6387" max="6387" width="31.28515625" style="1" customWidth="1"/>
-    <col min="6388" max="6627" width="9.140625" style="1"/>
-    <col min="6628" max="6628" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6629" max="6629" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6630" max="6630" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6631" max="6631" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6632" max="6632" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6633" max="6634" width="28.7109375" style="1" customWidth="1"/>
+    <col min="6380" max="6380" width="29.26953125" style="1" customWidth="1"/>
+    <col min="6381" max="6382" width="28.7265625" style="1" customWidth="1"/>
+    <col min="6383" max="6385" width="9.1796875" style="1"/>
+    <col min="6386" max="6386" width="36.81640625" style="1" customWidth="1"/>
+    <col min="6387" max="6387" width="31.26953125" style="1" customWidth="1"/>
+    <col min="6388" max="6627" width="9.1796875" style="1"/>
+    <col min="6628" max="6628" width="13.26953125" style="1" customWidth="1"/>
+    <col min="6629" max="6629" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6630" max="6630" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6631" max="6631" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6632" max="6632" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6633" max="6634" width="28.7265625" style="1" customWidth="1"/>
     <col min="6635" max="6635" width="29" style="1" customWidth="1"/>
-    <col min="6636" max="6636" width="29.28515625" style="1" customWidth="1"/>
-    <col min="6637" max="6638" width="28.7109375" style="1" customWidth="1"/>
-    <col min="6639" max="6641" width="9.140625" style="1"/>
-    <col min="6642" max="6642" width="36.85546875" style="1" customWidth="1"/>
-    <col min="6643" max="6643" width="31.28515625" style="1" customWidth="1"/>
-    <col min="6644" max="6883" width="9.140625" style="1"/>
-    <col min="6884" max="6884" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6885" max="6885" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6886" max="6886" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6887" max="6887" width="32.28515625" style="1" customWidth="1"/>
-    <col min="6888" max="6888" width="31.85546875" style="1" customWidth="1"/>
-    <col min="6889" max="6890" width="28.7109375" style="1" customWidth="1"/>
+    <col min="6636" max="6636" width="29.26953125" style="1" customWidth="1"/>
+    <col min="6637" max="6638" width="28.7265625" style="1" customWidth="1"/>
+    <col min="6639" max="6641" width="9.1796875" style="1"/>
+    <col min="6642" max="6642" width="36.81640625" style="1" customWidth="1"/>
+    <col min="6643" max="6643" width="31.26953125" style="1" customWidth="1"/>
+    <col min="6644" max="6883" width="9.1796875" style="1"/>
+    <col min="6884" max="6884" width="13.26953125" style="1" customWidth="1"/>
+    <col min="6885" max="6885" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6886" max="6886" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6887" max="6887" width="32.26953125" style="1" customWidth="1"/>
+    <col min="6888" max="6888" width="31.81640625" style="1" customWidth="1"/>
+    <col min="6889" max="6890" width="28.7265625" style="1" customWidth="1"/>
     <col min="6891" max="6891" width="29" style="1" customWidth="1"/>
-    <col min="6892" max="6892" width="29.28515625" style="1" customWidth="1"/>
-    <col min="6893" max="6894" width="28.7109375" style="1" customWidth="1"/>
-    <col min="6895" max="6897" width="9.140625" style="1"/>
-    <col min="6898" max="6898" width="36.85546875" style="1" customWidth="1"/>
-    <col min="6899" max="6899" width="31.28515625" style="1" customWidth="1"/>
-    <col min="6900" max="7139" width="9.140625" style="1"/>
-    <col min="7140" max="7140" width="13.28515625" style="1" customWidth="1"/>
-    <col min="7141" max="7141" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7142" max="7142" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7143" max="7143" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7144" max="7144" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7145" max="7146" width="28.7109375" style="1" customWidth="1"/>
+    <col min="6892" max="6892" width="29.26953125" style="1" customWidth="1"/>
+    <col min="6893" max="6894" width="28.7265625" style="1" customWidth="1"/>
+    <col min="6895" max="6897" width="9.1796875" style="1"/>
+    <col min="6898" max="6898" width="36.81640625" style="1" customWidth="1"/>
+    <col min="6899" max="6899" width="31.26953125" style="1" customWidth="1"/>
+    <col min="6900" max="7139" width="9.1796875" style="1"/>
+    <col min="7140" max="7140" width="13.26953125" style="1" customWidth="1"/>
+    <col min="7141" max="7141" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7142" max="7142" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7143" max="7143" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7144" max="7144" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7145" max="7146" width="28.7265625" style="1" customWidth="1"/>
     <col min="7147" max="7147" width="29" style="1" customWidth="1"/>
-    <col min="7148" max="7148" width="29.28515625" style="1" customWidth="1"/>
-    <col min="7149" max="7150" width="28.7109375" style="1" customWidth="1"/>
-    <col min="7151" max="7153" width="9.140625" style="1"/>
-    <col min="7154" max="7154" width="36.85546875" style="1" customWidth="1"/>
-    <col min="7155" max="7155" width="31.28515625" style="1" customWidth="1"/>
-    <col min="7156" max="7395" width="9.140625" style="1"/>
-    <col min="7396" max="7396" width="13.28515625" style="1" customWidth="1"/>
-    <col min="7397" max="7397" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7398" max="7398" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7399" max="7399" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7400" max="7400" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7401" max="7402" width="28.7109375" style="1" customWidth="1"/>
+    <col min="7148" max="7148" width="29.26953125" style="1" customWidth="1"/>
+    <col min="7149" max="7150" width="28.7265625" style="1" customWidth="1"/>
+    <col min="7151" max="7153" width="9.1796875" style="1"/>
+    <col min="7154" max="7154" width="36.81640625" style="1" customWidth="1"/>
+    <col min="7155" max="7155" width="31.26953125" style="1" customWidth="1"/>
+    <col min="7156" max="7395" width="9.1796875" style="1"/>
+    <col min="7396" max="7396" width="13.26953125" style="1" customWidth="1"/>
+    <col min="7397" max="7397" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7398" max="7398" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7399" max="7399" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7400" max="7400" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7401" max="7402" width="28.7265625" style="1" customWidth="1"/>
     <col min="7403" max="7403" width="29" style="1" customWidth="1"/>
-    <col min="7404" max="7404" width="29.28515625" style="1" customWidth="1"/>
-    <col min="7405" max="7406" width="28.7109375" style="1" customWidth="1"/>
-    <col min="7407" max="7409" width="9.140625" style="1"/>
-    <col min="7410" max="7410" width="36.85546875" style="1" customWidth="1"/>
-    <col min="7411" max="7411" width="31.28515625" style="1" customWidth="1"/>
-    <col min="7412" max="7651" width="9.140625" style="1"/>
-    <col min="7652" max="7652" width="13.28515625" style="1" customWidth="1"/>
-    <col min="7653" max="7653" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7654" max="7654" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7655" max="7655" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7656" max="7656" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7657" max="7658" width="28.7109375" style="1" customWidth="1"/>
+    <col min="7404" max="7404" width="29.26953125" style="1" customWidth="1"/>
+    <col min="7405" max="7406" width="28.7265625" style="1" customWidth="1"/>
+    <col min="7407" max="7409" width="9.1796875" style="1"/>
+    <col min="7410" max="7410" width="36.81640625" style="1" customWidth="1"/>
+    <col min="7411" max="7411" width="31.26953125" style="1" customWidth="1"/>
+    <col min="7412" max="7651" width="9.1796875" style="1"/>
+    <col min="7652" max="7652" width="13.26953125" style="1" customWidth="1"/>
+    <col min="7653" max="7653" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7654" max="7654" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7655" max="7655" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7656" max="7656" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7657" max="7658" width="28.7265625" style="1" customWidth="1"/>
     <col min="7659" max="7659" width="29" style="1" customWidth="1"/>
-    <col min="7660" max="7660" width="29.28515625" style="1" customWidth="1"/>
-    <col min="7661" max="7662" width="28.7109375" style="1" customWidth="1"/>
-    <col min="7663" max="7665" width="9.140625" style="1"/>
-    <col min="7666" max="7666" width="36.85546875" style="1" customWidth="1"/>
-    <col min="7667" max="7667" width="31.28515625" style="1" customWidth="1"/>
-    <col min="7668" max="7907" width="9.140625" style="1"/>
-    <col min="7908" max="7908" width="13.28515625" style="1" customWidth="1"/>
-    <col min="7909" max="7909" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7910" max="7910" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7911" max="7911" width="32.28515625" style="1" customWidth="1"/>
-    <col min="7912" max="7912" width="31.85546875" style="1" customWidth="1"/>
-    <col min="7913" max="7914" width="28.7109375" style="1" customWidth="1"/>
+    <col min="7660" max="7660" width="29.26953125" style="1" customWidth="1"/>
+    <col min="7661" max="7662" width="28.7265625" style="1" customWidth="1"/>
+    <col min="7663" max="7665" width="9.1796875" style="1"/>
+    <col min="7666" max="7666" width="36.81640625" style="1" customWidth="1"/>
+    <col min="7667" max="7667" width="31.26953125" style="1" customWidth="1"/>
+    <col min="7668" max="7907" width="9.1796875" style="1"/>
+    <col min="7908" max="7908" width="13.26953125" style="1" customWidth="1"/>
+    <col min="7909" max="7909" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7910" max="7910" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7911" max="7911" width="32.26953125" style="1" customWidth="1"/>
+    <col min="7912" max="7912" width="31.81640625" style="1" customWidth="1"/>
+    <col min="7913" max="7914" width="28.7265625" style="1" customWidth="1"/>
     <col min="7915" max="7915" width="29" style="1" customWidth="1"/>
-    <col min="7916" max="7916" width="29.28515625" style="1" customWidth="1"/>
-    <col min="7917" max="7918" width="28.7109375" style="1" customWidth="1"/>
-    <col min="7919" max="7921" width="9.140625" style="1"/>
-    <col min="7922" max="7922" width="36.85546875" style="1" customWidth="1"/>
-    <col min="7923" max="7923" width="31.28515625" style="1" customWidth="1"/>
-    <col min="7924" max="8163" width="9.140625" style="1"/>
-    <col min="8164" max="8164" width="13.28515625" style="1" customWidth="1"/>
-    <col min="8165" max="8165" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8166" max="8166" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8167" max="8167" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8168" max="8168" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8169" max="8170" width="28.7109375" style="1" customWidth="1"/>
+    <col min="7916" max="7916" width="29.26953125" style="1" customWidth="1"/>
+    <col min="7917" max="7918" width="28.7265625" style="1" customWidth="1"/>
+    <col min="7919" max="7921" width="9.1796875" style="1"/>
+    <col min="7922" max="7922" width="36.81640625" style="1" customWidth="1"/>
+    <col min="7923" max="7923" width="31.26953125" style="1" customWidth="1"/>
+    <col min="7924" max="8163" width="9.1796875" style="1"/>
+    <col min="8164" max="8164" width="13.26953125" style="1" customWidth="1"/>
+    <col min="8165" max="8165" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8166" max="8166" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8167" max="8167" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8168" max="8168" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8169" max="8170" width="28.7265625" style="1" customWidth="1"/>
     <col min="8171" max="8171" width="29" style="1" customWidth="1"/>
-    <col min="8172" max="8172" width="29.28515625" style="1" customWidth="1"/>
-    <col min="8173" max="8174" width="28.7109375" style="1" customWidth="1"/>
-    <col min="8175" max="8177" width="9.140625" style="1"/>
-    <col min="8178" max="8178" width="36.85546875" style="1" customWidth="1"/>
-    <col min="8179" max="8179" width="31.28515625" style="1" customWidth="1"/>
-    <col min="8180" max="8419" width="9.140625" style="1"/>
-    <col min="8420" max="8420" width="13.28515625" style="1" customWidth="1"/>
-    <col min="8421" max="8421" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8422" max="8422" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8423" max="8423" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8424" max="8424" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8425" max="8426" width="28.7109375" style="1" customWidth="1"/>
+    <col min="8172" max="8172" width="29.26953125" style="1" customWidth="1"/>
+    <col min="8173" max="8174" width="28.7265625" style="1" customWidth="1"/>
+    <col min="8175" max="8177" width="9.1796875" style="1"/>
+    <col min="8178" max="8178" width="36.81640625" style="1" customWidth="1"/>
+    <col min="8179" max="8179" width="31.26953125" style="1" customWidth="1"/>
+    <col min="8180" max="8419" width="9.1796875" style="1"/>
+    <col min="8420" max="8420" width="13.26953125" style="1" customWidth="1"/>
+    <col min="8421" max="8421" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8422" max="8422" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8423" max="8423" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8424" max="8424" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8425" max="8426" width="28.7265625" style="1" customWidth="1"/>
     <col min="8427" max="8427" width="29" style="1" customWidth="1"/>
-    <col min="8428" max="8428" width="29.28515625" style="1" customWidth="1"/>
-    <col min="8429" max="8430" width="28.7109375" style="1" customWidth="1"/>
-    <col min="8431" max="8433" width="9.140625" style="1"/>
-    <col min="8434" max="8434" width="36.85546875" style="1" customWidth="1"/>
-    <col min="8435" max="8435" width="31.28515625" style="1" customWidth="1"/>
-    <col min="8436" max="8675" width="9.140625" style="1"/>
-    <col min="8676" max="8676" width="13.28515625" style="1" customWidth="1"/>
-    <col min="8677" max="8677" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8678" max="8678" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8679" max="8679" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8680" max="8680" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8681" max="8682" width="28.7109375" style="1" customWidth="1"/>
+    <col min="8428" max="8428" width="29.26953125" style="1" customWidth="1"/>
+    <col min="8429" max="8430" width="28.7265625" style="1" customWidth="1"/>
+    <col min="8431" max="8433" width="9.1796875" style="1"/>
+    <col min="8434" max="8434" width="36.81640625" style="1" customWidth="1"/>
+    <col min="8435" max="8435" width="31.26953125" style="1" customWidth="1"/>
+    <col min="8436" max="8675" width="9.1796875" style="1"/>
+    <col min="8676" max="8676" width="13.26953125" style="1" customWidth="1"/>
+    <col min="8677" max="8677" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8678" max="8678" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8679" max="8679" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8680" max="8680" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8681" max="8682" width="28.7265625" style="1" customWidth="1"/>
     <col min="8683" max="8683" width="29" style="1" customWidth="1"/>
-    <col min="8684" max="8684" width="29.28515625" style="1" customWidth="1"/>
-    <col min="8685" max="8686" width="28.7109375" style="1" customWidth="1"/>
-    <col min="8687" max="8689" width="9.140625" style="1"/>
-    <col min="8690" max="8690" width="36.85546875" style="1" customWidth="1"/>
-    <col min="8691" max="8691" width="31.28515625" style="1" customWidth="1"/>
-    <col min="8692" max="8931" width="9.140625" style="1"/>
-    <col min="8932" max="8932" width="13.28515625" style="1" customWidth="1"/>
-    <col min="8933" max="8933" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8934" max="8934" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8935" max="8935" width="32.28515625" style="1" customWidth="1"/>
-    <col min="8936" max="8936" width="31.85546875" style="1" customWidth="1"/>
-    <col min="8937" max="8938" width="28.7109375" style="1" customWidth="1"/>
+    <col min="8684" max="8684" width="29.26953125" style="1" customWidth="1"/>
+    <col min="8685" max="8686" width="28.7265625" style="1" customWidth="1"/>
+    <col min="8687" max="8689" width="9.1796875" style="1"/>
+    <col min="8690" max="8690" width="36.81640625" style="1" customWidth="1"/>
+    <col min="8691" max="8691" width="31.26953125" style="1" customWidth="1"/>
+    <col min="8692" max="8931" width="9.1796875" style="1"/>
+    <col min="8932" max="8932" width="13.26953125" style="1" customWidth="1"/>
+    <col min="8933" max="8933" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8934" max="8934" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8935" max="8935" width="32.26953125" style="1" customWidth="1"/>
+    <col min="8936" max="8936" width="31.81640625" style="1" customWidth="1"/>
+    <col min="8937" max="8938" width="28.7265625" style="1" customWidth="1"/>
     <col min="8939" max="8939" width="29" style="1" customWidth="1"/>
-    <col min="8940" max="8940" width="29.28515625" style="1" customWidth="1"/>
-    <col min="8941" max="8942" width="28.7109375" style="1" customWidth="1"/>
-    <col min="8943" max="8945" width="9.140625" style="1"/>
-    <col min="8946" max="8946" width="36.85546875" style="1" customWidth="1"/>
-    <col min="8947" max="8947" width="31.28515625" style="1" customWidth="1"/>
-    <col min="8948" max="9187" width="9.140625" style="1"/>
-    <col min="9188" max="9188" width="13.28515625" style="1" customWidth="1"/>
-    <col min="9189" max="9189" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9190" max="9190" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9191" max="9191" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9192" max="9192" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9193" max="9194" width="28.7109375" style="1" customWidth="1"/>
+    <col min="8940" max="8940" width="29.26953125" style="1" customWidth="1"/>
+    <col min="8941" max="8942" width="28.7265625" style="1" customWidth="1"/>
+    <col min="8943" max="8945" width="9.1796875" style="1"/>
+    <col min="8946" max="8946" width="36.81640625" style="1" customWidth="1"/>
+    <col min="8947" max="8947" width="31.26953125" style="1" customWidth="1"/>
+    <col min="8948" max="9187" width="9.1796875" style="1"/>
+    <col min="9188" max="9188" width="13.26953125" style="1" customWidth="1"/>
+    <col min="9189" max="9189" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9190" max="9190" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9191" max="9191" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9192" max="9192" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9193" max="9194" width="28.7265625" style="1" customWidth="1"/>
     <col min="9195" max="9195" width="29" style="1" customWidth="1"/>
-    <col min="9196" max="9196" width="29.28515625" style="1" customWidth="1"/>
-    <col min="9197" max="9198" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9199" max="9201" width="9.140625" style="1"/>
-    <col min="9202" max="9202" width="36.85546875" style="1" customWidth="1"/>
-    <col min="9203" max="9203" width="31.28515625" style="1" customWidth="1"/>
-    <col min="9204" max="9443" width="9.140625" style="1"/>
-    <col min="9444" max="9444" width="13.28515625" style="1" customWidth="1"/>
-    <col min="9445" max="9445" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9446" max="9446" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9447" max="9447" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9448" max="9448" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9449" max="9450" width="28.7109375" style="1" customWidth="1"/>
+    <col min="9196" max="9196" width="29.26953125" style="1" customWidth="1"/>
+    <col min="9197" max="9198" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9199" max="9201" width="9.1796875" style="1"/>
+    <col min="9202" max="9202" width="36.81640625" style="1" customWidth="1"/>
+    <col min="9203" max="9203" width="31.26953125" style="1" customWidth="1"/>
+    <col min="9204" max="9443" width="9.1796875" style="1"/>
+    <col min="9444" max="9444" width="13.26953125" style="1" customWidth="1"/>
+    <col min="9445" max="9445" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9446" max="9446" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9447" max="9447" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9448" max="9448" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9449" max="9450" width="28.7265625" style="1" customWidth="1"/>
     <col min="9451" max="9451" width="29" style="1" customWidth="1"/>
-    <col min="9452" max="9452" width="29.28515625" style="1" customWidth="1"/>
-    <col min="9453" max="9454" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9455" max="9457" width="9.140625" style="1"/>
-    <col min="9458" max="9458" width="36.85546875" style="1" customWidth="1"/>
-    <col min="9459" max="9459" width="31.28515625" style="1" customWidth="1"/>
-    <col min="9460" max="9699" width="9.140625" style="1"/>
-    <col min="9700" max="9700" width="13.28515625" style="1" customWidth="1"/>
-    <col min="9701" max="9701" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9702" max="9702" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9703" max="9703" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9704" max="9704" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9705" max="9706" width="28.7109375" style="1" customWidth="1"/>
+    <col min="9452" max="9452" width="29.26953125" style="1" customWidth="1"/>
+    <col min="9453" max="9454" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9455" max="9457" width="9.1796875" style="1"/>
+    <col min="9458" max="9458" width="36.81640625" style="1" customWidth="1"/>
+    <col min="9459" max="9459" width="31.26953125" style="1" customWidth="1"/>
+    <col min="9460" max="9699" width="9.1796875" style="1"/>
+    <col min="9700" max="9700" width="13.26953125" style="1" customWidth="1"/>
+    <col min="9701" max="9701" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9702" max="9702" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9703" max="9703" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9704" max="9704" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9705" max="9706" width="28.7265625" style="1" customWidth="1"/>
     <col min="9707" max="9707" width="29" style="1" customWidth="1"/>
-    <col min="9708" max="9708" width="29.28515625" style="1" customWidth="1"/>
-    <col min="9709" max="9710" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9711" max="9713" width="9.140625" style="1"/>
-    <col min="9714" max="9714" width="36.85546875" style="1" customWidth="1"/>
-    <col min="9715" max="9715" width="31.28515625" style="1" customWidth="1"/>
-    <col min="9716" max="9955" width="9.140625" style="1"/>
-    <col min="9956" max="9956" width="13.28515625" style="1" customWidth="1"/>
-    <col min="9957" max="9957" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9958" max="9958" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9959" max="9959" width="32.28515625" style="1" customWidth="1"/>
-    <col min="9960" max="9960" width="31.85546875" style="1" customWidth="1"/>
-    <col min="9961" max="9962" width="28.7109375" style="1" customWidth="1"/>
+    <col min="9708" max="9708" width="29.26953125" style="1" customWidth="1"/>
+    <col min="9709" max="9710" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9711" max="9713" width="9.1796875" style="1"/>
+    <col min="9714" max="9714" width="36.81640625" style="1" customWidth="1"/>
+    <col min="9715" max="9715" width="31.26953125" style="1" customWidth="1"/>
+    <col min="9716" max="9955" width="9.1796875" style="1"/>
+    <col min="9956" max="9956" width="13.26953125" style="1" customWidth="1"/>
+    <col min="9957" max="9957" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9958" max="9958" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9959" max="9959" width="32.26953125" style="1" customWidth="1"/>
+    <col min="9960" max="9960" width="31.81640625" style="1" customWidth="1"/>
+    <col min="9961" max="9962" width="28.7265625" style="1" customWidth="1"/>
     <col min="9963" max="9963" width="29" style="1" customWidth="1"/>
-    <col min="9964" max="9964" width="29.28515625" style="1" customWidth="1"/>
-    <col min="9965" max="9966" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9967" max="9969" width="9.140625" style="1"/>
-    <col min="9970" max="9970" width="36.85546875" style="1" customWidth="1"/>
-    <col min="9971" max="9971" width="31.28515625" style="1" customWidth="1"/>
-    <col min="9972" max="10211" width="9.140625" style="1"/>
-    <col min="10212" max="10212" width="13.28515625" style="1" customWidth="1"/>
-    <col min="10213" max="10213" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10214" max="10214" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10215" max="10215" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10216" max="10216" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10217" max="10218" width="28.7109375" style="1" customWidth="1"/>
+    <col min="9964" max="9964" width="29.26953125" style="1" customWidth="1"/>
+    <col min="9965" max="9966" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9967" max="9969" width="9.1796875" style="1"/>
+    <col min="9970" max="9970" width="36.81640625" style="1" customWidth="1"/>
+    <col min="9971" max="9971" width="31.26953125" style="1" customWidth="1"/>
+    <col min="9972" max="10211" width="9.1796875" style="1"/>
+    <col min="10212" max="10212" width="13.26953125" style="1" customWidth="1"/>
+    <col min="10213" max="10213" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10214" max="10214" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10215" max="10215" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10216" max="10216" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10217" max="10218" width="28.7265625" style="1" customWidth="1"/>
     <col min="10219" max="10219" width="29" style="1" customWidth="1"/>
-    <col min="10220" max="10220" width="29.28515625" style="1" customWidth="1"/>
-    <col min="10221" max="10222" width="28.7109375" style="1" customWidth="1"/>
-    <col min="10223" max="10225" width="9.140625" style="1"/>
-    <col min="10226" max="10226" width="36.85546875" style="1" customWidth="1"/>
-    <col min="10227" max="10227" width="31.28515625" style="1" customWidth="1"/>
-    <col min="10228" max="10467" width="9.140625" style="1"/>
-    <col min="10468" max="10468" width="13.28515625" style="1" customWidth="1"/>
-    <col min="10469" max="10469" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10470" max="10470" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10471" max="10471" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10472" max="10472" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10473" max="10474" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10220" max="10220" width="29.26953125" style="1" customWidth="1"/>
+    <col min="10221" max="10222" width="28.7265625" style="1" customWidth="1"/>
+    <col min="10223" max="10225" width="9.1796875" style="1"/>
+    <col min="10226" max="10226" width="36.81640625" style="1" customWidth="1"/>
+    <col min="10227" max="10227" width="31.26953125" style="1" customWidth="1"/>
+    <col min="10228" max="10467" width="9.1796875" style="1"/>
+    <col min="10468" max="10468" width="13.26953125" style="1" customWidth="1"/>
+    <col min="10469" max="10469" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10470" max="10470" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10471" max="10471" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10472" max="10472" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10473" max="10474" width="28.7265625" style="1" customWidth="1"/>
     <col min="10475" max="10475" width="29" style="1" customWidth="1"/>
-    <col min="10476" max="10476" width="29.28515625" style="1" customWidth="1"/>
-    <col min="10477" max="10478" width="28.7109375" style="1" customWidth="1"/>
-    <col min="10479" max="10481" width="9.140625" style="1"/>
-    <col min="10482" max="10482" width="36.85546875" style="1" customWidth="1"/>
-    <col min="10483" max="10483" width="31.28515625" style="1" customWidth="1"/>
-    <col min="10484" max="10723" width="9.140625" style="1"/>
-    <col min="10724" max="10724" width="13.28515625" style="1" customWidth="1"/>
-    <col min="10725" max="10725" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10726" max="10726" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10727" max="10727" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10728" max="10728" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10729" max="10730" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10476" max="10476" width="29.26953125" style="1" customWidth="1"/>
+    <col min="10477" max="10478" width="28.7265625" style="1" customWidth="1"/>
+    <col min="10479" max="10481" width="9.1796875" style="1"/>
+    <col min="10482" max="10482" width="36.81640625" style="1" customWidth="1"/>
+    <col min="10483" max="10483" width="31.26953125" style="1" customWidth="1"/>
+    <col min="10484" max="10723" width="9.1796875" style="1"/>
+    <col min="10724" max="10724" width="13.26953125" style="1" customWidth="1"/>
+    <col min="10725" max="10725" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10726" max="10726" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10727" max="10727" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10728" max="10728" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10729" max="10730" width="28.7265625" style="1" customWidth="1"/>
     <col min="10731" max="10731" width="29" style="1" customWidth="1"/>
-    <col min="10732" max="10732" width="29.28515625" style="1" customWidth="1"/>
-    <col min="10733" max="10734" width="28.7109375" style="1" customWidth="1"/>
-    <col min="10735" max="10737" width="9.140625" style="1"/>
-    <col min="10738" max="10738" width="36.85546875" style="1" customWidth="1"/>
-    <col min="10739" max="10739" width="31.28515625" style="1" customWidth="1"/>
-    <col min="10740" max="10979" width="9.140625" style="1"/>
-    <col min="10980" max="10980" width="13.28515625" style="1" customWidth="1"/>
-    <col min="10981" max="10981" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10982" max="10982" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10983" max="10983" width="32.28515625" style="1" customWidth="1"/>
-    <col min="10984" max="10984" width="31.85546875" style="1" customWidth="1"/>
-    <col min="10985" max="10986" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10732" max="10732" width="29.26953125" style="1" customWidth="1"/>
+    <col min="10733" max="10734" width="28.7265625" style="1" customWidth="1"/>
+    <col min="10735" max="10737" width="9.1796875" style="1"/>
+    <col min="10738" max="10738" width="36.81640625" style="1" customWidth="1"/>
+    <col min="10739" max="10739" width="31.26953125" style="1" customWidth="1"/>
+    <col min="10740" max="10979" width="9.1796875" style="1"/>
+    <col min="10980" max="10980" width="13.26953125" style="1" customWidth="1"/>
+    <col min="10981" max="10981" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10982" max="10982" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10983" max="10983" width="32.26953125" style="1" customWidth="1"/>
+    <col min="10984" max="10984" width="31.81640625" style="1" customWidth="1"/>
+    <col min="10985" max="10986" width="28.7265625" style="1" customWidth="1"/>
     <col min="10987" max="10987" width="29" style="1" customWidth="1"/>
-    <col min="10988" max="10988" width="29.28515625" style="1" customWidth="1"/>
-    <col min="10989" max="10990" width="28.7109375" style="1" customWidth="1"/>
-    <col min="10991" max="10993" width="9.140625" style="1"/>
-    <col min="10994" max="10994" width="36.85546875" style="1" customWidth="1"/>
-    <col min="10995" max="10995" width="31.28515625" style="1" customWidth="1"/>
-    <col min="10996" max="11235" width="9.140625" style="1"/>
-    <col min="11236" max="11236" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11237" max="11237" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11238" max="11238" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11239" max="11239" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11240" max="11240" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11241" max="11242" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10988" max="10988" width="29.26953125" style="1" customWidth="1"/>
+    <col min="10989" max="10990" width="28.7265625" style="1" customWidth="1"/>
+    <col min="10991" max="10993" width="9.1796875" style="1"/>
+    <col min="10994" max="10994" width="36.81640625" style="1" customWidth="1"/>
+    <col min="10995" max="10995" width="31.26953125" style="1" customWidth="1"/>
+    <col min="10996" max="11235" width="9.1796875" style="1"/>
+    <col min="11236" max="11236" width="13.26953125" style="1" customWidth="1"/>
+    <col min="11237" max="11237" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11238" max="11238" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11239" max="11239" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11240" max="11240" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11241" max="11242" width="28.7265625" style="1" customWidth="1"/>
     <col min="11243" max="11243" width="29" style="1" customWidth="1"/>
-    <col min="11244" max="11244" width="29.28515625" style="1" customWidth="1"/>
-    <col min="11245" max="11246" width="28.7109375" style="1" customWidth="1"/>
-    <col min="11247" max="11249" width="9.140625" style="1"/>
-    <col min="11250" max="11250" width="36.85546875" style="1" customWidth="1"/>
-    <col min="11251" max="11251" width="31.28515625" style="1" customWidth="1"/>
-    <col min="11252" max="11491" width="9.140625" style="1"/>
-    <col min="11492" max="11492" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11493" max="11493" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11494" max="11494" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11495" max="11495" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11496" max="11496" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11497" max="11498" width="28.7109375" style="1" customWidth="1"/>
+    <col min="11244" max="11244" width="29.26953125" style="1" customWidth="1"/>
+    <col min="11245" max="11246" width="28.7265625" style="1" customWidth="1"/>
+    <col min="11247" max="11249" width="9.1796875" style="1"/>
+    <col min="11250" max="11250" width="36.81640625" style="1" customWidth="1"/>
+    <col min="11251" max="11251" width="31.26953125" style="1" customWidth="1"/>
+    <col min="11252" max="11491" width="9.1796875" style="1"/>
+    <col min="11492" max="11492" width="13.26953125" style="1" customWidth="1"/>
+    <col min="11493" max="11493" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11494" max="11494" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11495" max="11495" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11496" max="11496" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11497" max="11498" width="28.7265625" style="1" customWidth="1"/>
     <col min="11499" max="11499" width="29" style="1" customWidth="1"/>
-    <col min="11500" max="11500" width="29.28515625" style="1" customWidth="1"/>
-    <col min="11501" max="11502" width="28.7109375" style="1" customWidth="1"/>
-    <col min="11503" max="11505" width="9.140625" style="1"/>
-    <col min="11506" max="11506" width="36.85546875" style="1" customWidth="1"/>
-    <col min="11507" max="11507" width="31.28515625" style="1" customWidth="1"/>
-    <col min="11508" max="11747" width="9.140625" style="1"/>
-    <col min="11748" max="11748" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11749" max="11749" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11750" max="11750" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11751" max="11751" width="32.28515625" style="1" customWidth="1"/>
-    <col min="11752" max="11752" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11753" max="11754" width="28.7109375" style="1" customWidth="1"/>
+    <col min="11500" max="11500" width="29.26953125" style="1" customWidth="1"/>
+    <col min="11501" max="11502" width="28.7265625" style="1" customWidth="1"/>
+    <col min="11503" max="11505" width="9.1796875" style="1"/>
+    <col min="11506" max="11506" width="36.81640625" style="1" customWidth="1"/>
+    <col min="11507" max="11507" width="31.26953125" style="1" customWidth="1"/>
+    <col min="11508" max="11747" width="9.1796875" style="1"/>
+    <col min="11748" max="11748" width="13.26953125" style="1" customWidth="1"/>
+    <col min="11749" max="11749" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11750" max="11750" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11751" max="11751" width="32.26953125" style="1" customWidth="1"/>
+    <col min="11752" max="11752" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11753" max="11754" width="28.7265625" style="1" customWidth="1"/>
     <col min="11755" max="11755" width="29" style="1" customWidth="1"/>
-    <col min="11756" max="11756" width="29.28515625" style="1" customWidth="1"/>
-    <col min="11757" max="11758" width="28.7109375" style="1" customWidth="1"/>
-    <col min="11759" max="11761" width="9.140625" style="1"/>
-    <col min="11762" max="11762" width="36.85546875" style="1" customWidth="1"/>
-    <col min="11763" max="11763" width="31.28515625" style="1" customWidth="1"/>
-    <col min="11764" max="12003" width="9.140625" style="1"/>
-    <col min="12004" max="12004" width="13.28515625" style="1" customWidth="1"/>
-    <col min="12005" max="12005" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12006" max="12006" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12007" max="12007" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12008" max="12008" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12009" max="12010" width="28.7109375" style="1" customWidth="1"/>
+    <col min="11756" max="11756" width="29.26953125" style="1" customWidth="1"/>
+    <col min="11757" max="11758" width="28.7265625" style="1" customWidth="1"/>
+    <col min="11759" max="11761" width="9.1796875" style="1"/>
+    <col min="11762" max="11762" width="36.81640625" style="1" customWidth="1"/>
+    <col min="11763" max="11763" width="31.26953125" style="1" customWidth="1"/>
+    <col min="11764" max="12003" width="9.1796875" style="1"/>
+    <col min="12004" max="12004" width="13.26953125" style="1" customWidth="1"/>
+    <col min="12005" max="12005" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12006" max="12006" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12007" max="12007" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12008" max="12008" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12009" max="12010" width="28.7265625" style="1" customWidth="1"/>
     <col min="12011" max="12011" width="29" style="1" customWidth="1"/>
-    <col min="12012" max="12012" width="29.28515625" style="1" customWidth="1"/>
-    <col min="12013" max="12014" width="28.7109375" style="1" customWidth="1"/>
-    <col min="12015" max="12017" width="9.140625" style="1"/>
-    <col min="12018" max="12018" width="36.85546875" style="1" customWidth="1"/>
-    <col min="12019" max="12019" width="31.28515625" style="1" customWidth="1"/>
-    <col min="12020" max="12259" width="9.140625" style="1"/>
-    <col min="12260" max="12260" width="13.28515625" style="1" customWidth="1"/>
-    <col min="12261" max="12261" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12262" max="12262" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12263" max="12263" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12264" max="12264" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12265" max="12266" width="28.7109375" style="1" customWidth="1"/>
+    <col min="12012" max="12012" width="29.26953125" style="1" customWidth="1"/>
+    <col min="12013" max="12014" width="28.7265625" style="1" customWidth="1"/>
+    <col min="12015" max="12017" width="9.1796875" style="1"/>
+    <col min="12018" max="12018" width="36.81640625" style="1" customWidth="1"/>
+    <col min="12019" max="12019" width="31.26953125" style="1" customWidth="1"/>
+    <col min="12020" max="12259" width="9.1796875" style="1"/>
+    <col min="12260" max="12260" width="13.26953125" style="1" customWidth="1"/>
+    <col min="12261" max="12261" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12262" max="12262" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12263" max="12263" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12264" max="12264" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12265" max="12266" width="28.7265625" style="1" customWidth="1"/>
     <col min="12267" max="12267" width="29" style="1" customWidth="1"/>
-    <col min="12268" max="12268" width="29.28515625" style="1" customWidth="1"/>
-    <col min="12269" max="12270" width="28.7109375" style="1" customWidth="1"/>
-    <col min="12271" max="12273" width="9.140625" style="1"/>
-    <col min="12274" max="12274" width="36.85546875" style="1" customWidth="1"/>
-    <col min="12275" max="12275" width="31.28515625" style="1" customWidth="1"/>
-    <col min="12276" max="12515" width="9.140625" style="1"/>
-    <col min="12516" max="12516" width="13.28515625" style="1" customWidth="1"/>
-    <col min="12517" max="12517" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12518" max="12518" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12519" max="12519" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12520" max="12520" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12521" max="12522" width="28.7109375" style="1" customWidth="1"/>
+    <col min="12268" max="12268" width="29.26953125" style="1" customWidth="1"/>
+    <col min="12269" max="12270" width="28.7265625" style="1" customWidth="1"/>
+    <col min="12271" max="12273" width="9.1796875" style="1"/>
+    <col min="12274" max="12274" width="36.81640625" style="1" customWidth="1"/>
+    <col min="12275" max="12275" width="31.26953125" style="1" customWidth="1"/>
+    <col min="12276" max="12515" width="9.1796875" style="1"/>
+    <col min="12516" max="12516" width="13.26953125" style="1" customWidth="1"/>
+    <col min="12517" max="12517" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12518" max="12518" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12519" max="12519" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12520" max="12520" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12521" max="12522" width="28.7265625" style="1" customWidth="1"/>
     <col min="12523" max="12523" width="29" style="1" customWidth="1"/>
-    <col min="12524" max="12524" width="29.28515625" style="1" customWidth="1"/>
-    <col min="12525" max="12526" width="28.7109375" style="1" customWidth="1"/>
-    <col min="12527" max="12529" width="9.140625" style="1"/>
-    <col min="12530" max="12530" width="36.85546875" style="1" customWidth="1"/>
-    <col min="12531" max="12531" width="31.28515625" style="1" customWidth="1"/>
-    <col min="12532" max="12771" width="9.140625" style="1"/>
-    <col min="12772" max="12772" width="13.28515625" style="1" customWidth="1"/>
-    <col min="12773" max="12773" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12774" max="12774" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12775" max="12775" width="32.28515625" style="1" customWidth="1"/>
-    <col min="12776" max="12776" width="31.85546875" style="1" customWidth="1"/>
-    <col min="12777" max="12778" width="28.7109375" style="1" customWidth="1"/>
+    <col min="12524" max="12524" width="29.26953125" style="1" customWidth="1"/>
+    <col min="12525" max="12526" width="28.7265625" style="1" customWidth="1"/>
+    <col min="12527" max="12529" width="9.1796875" style="1"/>
+    <col min="12530" max="12530" width="36.81640625" style="1" customWidth="1"/>
+    <col min="12531" max="12531" width="31.26953125" style="1" customWidth="1"/>
+    <col min="12532" max="12771" width="9.1796875" style="1"/>
+    <col min="12772" max="12772" width="13.26953125" style="1" customWidth="1"/>
+    <col min="12773" max="12773" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12774" max="12774" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12775" max="12775" width="32.26953125" style="1" customWidth="1"/>
+    <col min="12776" max="12776" width="31.81640625" style="1" customWidth="1"/>
+    <col min="12777" max="12778" width="28.7265625" style="1" customWidth="1"/>
     <col min="12779" max="12779" width="29" style="1" customWidth="1"/>
-    <col min="12780" max="12780" width="29.28515625" style="1" customWidth="1"/>
-    <col min="12781" max="12782" width="28.7109375" style="1" customWidth="1"/>
-    <col min="12783" max="12785" width="9.140625" style="1"/>
-    <col min="12786" max="12786" width="36.85546875" style="1" customWidth="1"/>
-    <col min="12787" max="12787" width="31.28515625" style="1" customWidth="1"/>
-    <col min="12788" max="13027" width="9.140625" style="1"/>
-    <col min="13028" max="13028" width="13.28515625" style="1" customWidth="1"/>
-    <col min="13029" max="13029" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13030" max="13030" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13031" max="13031" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13032" max="13032" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13033" max="13034" width="28.7109375" style="1" customWidth="1"/>
+    <col min="12780" max="12780" width="29.26953125" style="1" customWidth="1"/>
+    <col min="12781" max="12782" width="28.7265625" style="1" customWidth="1"/>
+    <col min="12783" max="12785" width="9.1796875" style="1"/>
+    <col min="12786" max="12786" width="36.81640625" style="1" customWidth="1"/>
+    <col min="12787" max="12787" width="31.26953125" style="1" customWidth="1"/>
+    <col min="12788" max="13027" width="9.1796875" style="1"/>
+    <col min="13028" max="13028" width="13.26953125" style="1" customWidth="1"/>
+    <col min="13029" max="13029" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13030" max="13030" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13031" max="13031" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13032" max="13032" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13033" max="13034" width="28.7265625" style="1" customWidth="1"/>
     <col min="13035" max="13035" width="29" style="1" customWidth="1"/>
-    <col min="13036" max="13036" width="29.28515625" style="1" customWidth="1"/>
-    <col min="13037" max="13038" width="28.7109375" style="1" customWidth="1"/>
-    <col min="13039" max="13041" width="9.140625" style="1"/>
-    <col min="13042" max="13042" width="36.85546875" style="1" customWidth="1"/>
-    <col min="13043" max="13043" width="31.28515625" style="1" customWidth="1"/>
-    <col min="13044" max="13283" width="9.140625" style="1"/>
-    <col min="13284" max="13284" width="13.28515625" style="1" customWidth="1"/>
-    <col min="13285" max="13285" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13286" max="13286" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13287" max="13287" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13288" max="13288" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13289" max="13290" width="28.7109375" style="1" customWidth="1"/>
+    <col min="13036" max="13036" width="29.26953125" style="1" customWidth="1"/>
+    <col min="13037" max="13038" width="28.7265625" style="1" customWidth="1"/>
+    <col min="13039" max="13041" width="9.1796875" style="1"/>
+    <col min="13042" max="13042" width="36.81640625" style="1" customWidth="1"/>
+    <col min="13043" max="13043" width="31.26953125" style="1" customWidth="1"/>
+    <col min="13044" max="13283" width="9.1796875" style="1"/>
+    <col min="13284" max="13284" width="13.26953125" style="1" customWidth="1"/>
+    <col min="13285" max="13285" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13286" max="13286" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13287" max="13287" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13288" max="13288" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13289" max="13290" width="28.7265625" style="1" customWidth="1"/>
     <col min="13291" max="13291" width="29" style="1" customWidth="1"/>
-    <col min="13292" max="13292" width="29.28515625" style="1" customWidth="1"/>
-    <col min="13293" max="13294" width="28.7109375" style="1" customWidth="1"/>
-    <col min="13295" max="13297" width="9.140625" style="1"/>
-    <col min="13298" max="13298" width="36.85546875" style="1" customWidth="1"/>
-    <col min="13299" max="13299" width="31.28515625" style="1" customWidth="1"/>
-    <col min="13300" max="13539" width="9.140625" style="1"/>
-    <col min="13540" max="13540" width="13.28515625" style="1" customWidth="1"/>
-    <col min="13541" max="13541" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13542" max="13542" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13543" max="13543" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13544" max="13544" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13545" max="13546" width="28.7109375" style="1" customWidth="1"/>
+    <col min="13292" max="13292" width="29.26953125" style="1" customWidth="1"/>
+    <col min="13293" max="13294" width="28.7265625" style="1" customWidth="1"/>
+    <col min="13295" max="13297" width="9.1796875" style="1"/>
+    <col min="13298" max="13298" width="36.81640625" style="1" customWidth="1"/>
+    <col min="13299" max="13299" width="31.26953125" style="1" customWidth="1"/>
+    <col min="13300" max="13539" width="9.1796875" style="1"/>
+    <col min="13540" max="13540" width="13.26953125" style="1" customWidth="1"/>
+    <col min="13541" max="13541" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13542" max="13542" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13543" max="13543" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13544" max="13544" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13545" max="13546" width="28.7265625" style="1" customWidth="1"/>
     <col min="13547" max="13547" width="29" style="1" customWidth="1"/>
-    <col min="13548" max="13548" width="29.28515625" style="1" customWidth="1"/>
-    <col min="13549" max="13550" width="28.7109375" style="1" customWidth="1"/>
-    <col min="13551" max="13553" width="9.140625" style="1"/>
-    <col min="13554" max="13554" width="36.85546875" style="1" customWidth="1"/>
-    <col min="13555" max="13555" width="31.28515625" style="1" customWidth="1"/>
-    <col min="13556" max="13795" width="9.140625" style="1"/>
-    <col min="13796" max="13796" width="13.28515625" style="1" customWidth="1"/>
-    <col min="13797" max="13797" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13798" max="13798" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13799" max="13799" width="32.28515625" style="1" customWidth="1"/>
-    <col min="13800" max="13800" width="31.85546875" style="1" customWidth="1"/>
-    <col min="13801" max="13802" width="28.7109375" style="1" customWidth="1"/>
+    <col min="13548" max="13548" width="29.26953125" style="1" customWidth="1"/>
+    <col min="13549" max="13550" width="28.7265625" style="1" customWidth="1"/>
+    <col min="13551" max="13553" width="9.1796875" style="1"/>
+    <col min="13554" max="13554" width="36.81640625" style="1" customWidth="1"/>
+    <col min="13555" max="13555" width="31.26953125" style="1" customWidth="1"/>
+    <col min="13556" max="13795" width="9.1796875" style="1"/>
+    <col min="13796" max="13796" width="13.26953125" style="1" customWidth="1"/>
+    <col min="13797" max="13797" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13798" max="13798" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13799" max="13799" width="32.26953125" style="1" customWidth="1"/>
+    <col min="13800" max="13800" width="31.81640625" style="1" customWidth="1"/>
+    <col min="13801" max="13802" width="28.7265625" style="1" customWidth="1"/>
     <col min="13803" max="13803" width="29" style="1" customWidth="1"/>
-    <col min="13804" max="13804" width="29.28515625" style="1" customWidth="1"/>
-    <col min="13805" max="13806" width="28.7109375" style="1" customWidth="1"/>
-    <col min="13807" max="13809" width="9.140625" style="1"/>
-    <col min="13810" max="13810" width="36.85546875" style="1" customWidth="1"/>
-    <col min="13811" max="13811" width="31.28515625" style="1" customWidth="1"/>
-    <col min="13812" max="14051" width="9.140625" style="1"/>
-    <col min="14052" max="14052" width="13.28515625" style="1" customWidth="1"/>
-    <col min="14053" max="14053" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14054" max="14054" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14055" max="14055" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14056" max="14056" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14057" max="14058" width="28.7109375" style="1" customWidth="1"/>
+    <col min="13804" max="13804" width="29.26953125" style="1" customWidth="1"/>
+    <col min="13805" max="13806" width="28.7265625" style="1" customWidth="1"/>
+    <col min="13807" max="13809" width="9.1796875" style="1"/>
+    <col min="13810" max="13810" width="36.81640625" style="1" customWidth="1"/>
+    <col min="13811" max="13811" width="31.26953125" style="1" customWidth="1"/>
+    <col min="13812" max="14051" width="9.1796875" style="1"/>
+    <col min="14052" max="14052" width="13.26953125" style="1" customWidth="1"/>
+    <col min="14053" max="14053" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14054" max="14054" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14055" max="14055" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14056" max="14056" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14057" max="14058" width="28.7265625" style="1" customWidth="1"/>
     <col min="14059" max="14059" width="29" style="1" customWidth="1"/>
-    <col min="14060" max="14060" width="29.28515625" style="1" customWidth="1"/>
-    <col min="14061" max="14062" width="28.7109375" style="1" customWidth="1"/>
-    <col min="14063" max="14065" width="9.140625" style="1"/>
-    <col min="14066" max="14066" width="36.85546875" style="1" customWidth="1"/>
-    <col min="14067" max="14067" width="31.28515625" style="1" customWidth="1"/>
-    <col min="14068" max="14307" width="9.140625" style="1"/>
-    <col min="14308" max="14308" width="13.28515625" style="1" customWidth="1"/>
-    <col min="14309" max="14309" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14310" max="14310" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14311" max="14311" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14312" max="14312" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14313" max="14314" width="28.7109375" style="1" customWidth="1"/>
+    <col min="14060" max="14060" width="29.26953125" style="1" customWidth="1"/>
+    <col min="14061" max="14062" width="28.7265625" style="1" customWidth="1"/>
+    <col min="14063" max="14065" width="9.1796875" style="1"/>
+    <col min="14066" max="14066" width="36.81640625" style="1" customWidth="1"/>
+    <col min="14067" max="14067" width="31.26953125" style="1" customWidth="1"/>
+    <col min="14068" max="14307" width="9.1796875" style="1"/>
+    <col min="14308" max="14308" width="13.26953125" style="1" customWidth="1"/>
+    <col min="14309" max="14309" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14310" max="14310" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14311" max="14311" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14312" max="14312" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14313" max="14314" width="28.7265625" style="1" customWidth="1"/>
     <col min="14315" max="14315" width="29" style="1" customWidth="1"/>
-    <col min="14316" max="14316" width="29.28515625" style="1" customWidth="1"/>
-    <col min="14317" max="14318" width="28.7109375" style="1" customWidth="1"/>
-    <col min="14319" max="14321" width="9.140625" style="1"/>
-    <col min="14322" max="14322" width="36.85546875" style="1" customWidth="1"/>
-    <col min="14323" max="14323" width="31.28515625" style="1" customWidth="1"/>
-    <col min="14324" max="14563" width="9.140625" style="1"/>
-    <col min="14564" max="14564" width="13.28515625" style="1" customWidth="1"/>
-    <col min="14565" max="14565" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14566" max="14566" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14567" max="14567" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14568" max="14568" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14569" max="14570" width="28.7109375" style="1" customWidth="1"/>
+    <col min="14316" max="14316" width="29.26953125" style="1" customWidth="1"/>
+    <col min="14317" max="14318" width="28.7265625" style="1" customWidth="1"/>
+    <col min="14319" max="14321" width="9.1796875" style="1"/>
+    <col min="14322" max="14322" width="36.81640625" style="1" customWidth="1"/>
+    <col min="14323" max="14323" width="31.26953125" style="1" customWidth="1"/>
+    <col min="14324" max="14563" width="9.1796875" style="1"/>
+    <col min="14564" max="14564" width="13.26953125" style="1" customWidth="1"/>
+    <col min="14565" max="14565" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14566" max="14566" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14567" max="14567" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14568" max="14568" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14569" max="14570" width="28.7265625" style="1" customWidth="1"/>
     <col min="14571" max="14571" width="29" style="1" customWidth="1"/>
-    <col min="14572" max="14572" width="29.28515625" style="1" customWidth="1"/>
-    <col min="14573" max="14574" width="28.7109375" style="1" customWidth="1"/>
-    <col min="14575" max="14577" width="9.140625" style="1"/>
-    <col min="14578" max="14578" width="36.85546875" style="1" customWidth="1"/>
-    <col min="14579" max="14579" width="31.28515625" style="1" customWidth="1"/>
-    <col min="14580" max="14819" width="9.140625" style="1"/>
-    <col min="14820" max="14820" width="13.28515625" style="1" customWidth="1"/>
-    <col min="14821" max="14821" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14822" max="14822" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14823" max="14823" width="32.28515625" style="1" customWidth="1"/>
-    <col min="14824" max="14824" width="31.85546875" style="1" customWidth="1"/>
-    <col min="14825" max="14826" width="28.7109375" style="1" customWidth="1"/>
+    <col min="14572" max="14572" width="29.26953125" style="1" customWidth="1"/>
+    <col min="14573" max="14574" width="28.7265625" style="1" customWidth="1"/>
+    <col min="14575" max="14577" width="9.1796875" style="1"/>
+    <col min="14578" max="14578" width="36.81640625" style="1" customWidth="1"/>
+    <col min="14579" max="14579" width="31.26953125" style="1" customWidth="1"/>
+    <col min="14580" max="14819" width="9.1796875" style="1"/>
+    <col min="14820" max="14820" width="13.26953125" style="1" customWidth="1"/>
+    <col min="14821" max="14821" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14822" max="14822" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14823" max="14823" width="32.26953125" style="1" customWidth="1"/>
+    <col min="14824" max="14824" width="31.81640625" style="1" customWidth="1"/>
+    <col min="14825" max="14826" width="28.7265625" style="1" customWidth="1"/>
     <col min="14827" max="14827" width="29" style="1" customWidth="1"/>
-    <col min="14828" max="14828" width="29.28515625" style="1" customWidth="1"/>
-    <col min="14829" max="14830" width="28.7109375" style="1" customWidth="1"/>
-    <col min="14831" max="14833" width="9.140625" style="1"/>
-    <col min="14834" max="14834" width="36.85546875" style="1" customWidth="1"/>
-    <col min="14835" max="14835" width="31.28515625" style="1" customWidth="1"/>
-    <col min="14836" max="15075" width="9.140625" style="1"/>
-    <col min="15076" max="15076" width="13.28515625" style="1" customWidth="1"/>
-    <col min="15077" max="15077" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15078" max="15078" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15079" max="15079" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15080" max="15080" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15081" max="15082" width="28.7109375" style="1" customWidth="1"/>
+    <col min="14828" max="14828" width="29.26953125" style="1" customWidth="1"/>
+    <col min="14829" max="14830" width="28.7265625" style="1" customWidth="1"/>
+    <col min="14831" max="14833" width="9.1796875" style="1"/>
+    <col min="14834" max="14834" width="36.81640625" style="1" customWidth="1"/>
+    <col min="14835" max="14835" width="31.26953125" style="1" customWidth="1"/>
+    <col min="14836" max="15075" width="9.1796875" style="1"/>
+    <col min="15076" max="15076" width="13.26953125" style="1" customWidth="1"/>
+    <col min="15077" max="15077" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15078" max="15078" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15079" max="15079" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15080" max="15080" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15081" max="15082" width="28.7265625" style="1" customWidth="1"/>
     <col min="15083" max="15083" width="29" style="1" customWidth="1"/>
-    <col min="15084" max="15084" width="29.28515625" style="1" customWidth="1"/>
-    <col min="15085" max="15086" width="28.7109375" style="1" customWidth="1"/>
-    <col min="15087" max="15089" width="9.140625" style="1"/>
-    <col min="15090" max="15090" width="36.85546875" style="1" customWidth="1"/>
-    <col min="15091" max="15091" width="31.28515625" style="1" customWidth="1"/>
-    <col min="15092" max="15331" width="9.140625" style="1"/>
-    <col min="15332" max="15332" width="13.28515625" style="1" customWidth="1"/>
-    <col min="15333" max="15333" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15334" max="15334" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15335" max="15335" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15336" max="15336" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15337" max="15338" width="28.7109375" style="1" customWidth="1"/>
+    <col min="15084" max="15084" width="29.26953125" style="1" customWidth="1"/>
+    <col min="15085" max="15086" width="28.7265625" style="1" customWidth="1"/>
+    <col min="15087" max="15089" width="9.1796875" style="1"/>
+    <col min="15090" max="15090" width="36.81640625" style="1" customWidth="1"/>
+    <col min="15091" max="15091" width="31.26953125" style="1" customWidth="1"/>
+    <col min="15092" max="15331" width="9.1796875" style="1"/>
+    <col min="15332" max="15332" width="13.26953125" style="1" customWidth="1"/>
+    <col min="15333" max="15333" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15334" max="15334" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15335" max="15335" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15336" max="15336" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15337" max="15338" width="28.7265625" style="1" customWidth="1"/>
     <col min="15339" max="15339" width="29" style="1" customWidth="1"/>
-    <col min="15340" max="15340" width="29.28515625" style="1" customWidth="1"/>
-    <col min="15341" max="15342" width="28.7109375" style="1" customWidth="1"/>
-    <col min="15343" max="15345" width="9.140625" style="1"/>
-    <col min="15346" max="15346" width="36.85546875" style="1" customWidth="1"/>
-    <col min="15347" max="15347" width="31.28515625" style="1" customWidth="1"/>
-    <col min="15348" max="15587" width="9.140625" style="1"/>
-    <col min="15588" max="15588" width="13.28515625" style="1" customWidth="1"/>
-    <col min="15589" max="15589" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15590" max="15590" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15591" max="15591" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15592" max="15592" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15593" max="15594" width="28.7109375" style="1" customWidth="1"/>
+    <col min="15340" max="15340" width="29.26953125" style="1" customWidth="1"/>
+    <col min="15341" max="15342" width="28.7265625" style="1" customWidth="1"/>
+    <col min="15343" max="15345" width="9.1796875" style="1"/>
+    <col min="15346" max="15346" width="36.81640625" style="1" customWidth="1"/>
+    <col min="15347" max="15347" width="31.26953125" style="1" customWidth="1"/>
+    <col min="15348" max="15587" width="9.1796875" style="1"/>
+    <col min="15588" max="15588" width="13.26953125" style="1" customWidth="1"/>
+    <col min="15589" max="15589" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15590" max="15590" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15591" max="15591" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15592" max="15592" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15593" max="15594" width="28.7265625" style="1" customWidth="1"/>
     <col min="15595" max="15595" width="29" style="1" customWidth="1"/>
-    <col min="15596" max="15596" width="29.28515625" style="1" customWidth="1"/>
-    <col min="15597" max="15598" width="28.7109375" style="1" customWidth="1"/>
-    <col min="15599" max="15601" width="9.140625" style="1"/>
-    <col min="15602" max="15602" width="36.85546875" style="1" customWidth="1"/>
-    <col min="15603" max="15603" width="31.28515625" style="1" customWidth="1"/>
-    <col min="15604" max="15843" width="9.140625" style="1"/>
-    <col min="15844" max="15844" width="13.28515625" style="1" customWidth="1"/>
-    <col min="15845" max="15845" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15846" max="15846" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15847" max="15847" width="32.28515625" style="1" customWidth="1"/>
-    <col min="15848" max="15848" width="31.85546875" style="1" customWidth="1"/>
-    <col min="15849" max="15850" width="28.7109375" style="1" customWidth="1"/>
+    <col min="15596" max="15596" width="29.26953125" style="1" customWidth="1"/>
+    <col min="15597" max="15598" width="28.7265625" style="1" customWidth="1"/>
+    <col min="15599" max="15601" width="9.1796875" style="1"/>
+    <col min="15602" max="15602" width="36.81640625" style="1" customWidth="1"/>
+    <col min="15603" max="15603" width="31.26953125" style="1" customWidth="1"/>
+    <col min="15604" max="15843" width="9.1796875" style="1"/>
+    <col min="15844" max="15844" width="13.26953125" style="1" customWidth="1"/>
+    <col min="15845" max="15845" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15846" max="15846" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15847" max="15847" width="32.26953125" style="1" customWidth="1"/>
+    <col min="15848" max="15848" width="31.81640625" style="1" customWidth="1"/>
+    <col min="15849" max="15850" width="28.7265625" style="1" customWidth="1"/>
     <col min="15851" max="15851" width="29" style="1" customWidth="1"/>
-    <col min="15852" max="15852" width="29.28515625" style="1" customWidth="1"/>
-    <col min="15853" max="15854" width="28.7109375" style="1" customWidth="1"/>
-    <col min="15855" max="15857" width="9.140625" style="1"/>
-    <col min="15858" max="15858" width="36.85546875" style="1" customWidth="1"/>
-    <col min="15859" max="15859" width="31.28515625" style="1" customWidth="1"/>
-    <col min="15860" max="16099" width="9.140625" style="1"/>
-    <col min="16100" max="16100" width="13.28515625" style="1" customWidth="1"/>
-    <col min="16101" max="16101" width="32.28515625" style="1" customWidth="1"/>
-    <col min="16102" max="16102" width="31.85546875" style="1" customWidth="1"/>
-    <col min="16103" max="16103" width="32.28515625" style="1" customWidth="1"/>
-    <col min="16104" max="16104" width="31.85546875" style="1" customWidth="1"/>
-    <col min="16105" max="16106" width="28.7109375" style="1" customWidth="1"/>
+    <col min="15852" max="15852" width="29.26953125" style="1" customWidth="1"/>
+    <col min="15853" max="15854" width="28.7265625" style="1" customWidth="1"/>
+    <col min="15855" max="15857" width="9.1796875" style="1"/>
+    <col min="15858" max="15858" width="36.81640625" style="1" customWidth="1"/>
+    <col min="15859" max="15859" width="31.26953125" style="1" customWidth="1"/>
+    <col min="15860" max="16099" width="9.1796875" style="1"/>
+    <col min="16100" max="16100" width="13.26953125" style="1" customWidth="1"/>
+    <col min="16101" max="16101" width="32.26953125" style="1" customWidth="1"/>
+    <col min="16102" max="16102" width="31.81640625" style="1" customWidth="1"/>
+    <col min="16103" max="16103" width="32.26953125" style="1" customWidth="1"/>
+    <col min="16104" max="16104" width="31.81640625" style="1" customWidth="1"/>
+    <col min="16105" max="16106" width="28.7265625" style="1" customWidth="1"/>
     <col min="16107" max="16107" width="29" style="1" customWidth="1"/>
-    <col min="16108" max="16108" width="29.28515625" style="1" customWidth="1"/>
-    <col min="16109" max="16110" width="28.7109375" style="1" customWidth="1"/>
-    <col min="16111" max="16113" width="9.140625" style="1"/>
-    <col min="16114" max="16114" width="36.85546875" style="1" customWidth="1"/>
-    <col min="16115" max="16115" width="31.28515625" style="1" customWidth="1"/>
-    <col min="16116" max="16384" width="9.140625" style="1"/>
+    <col min="16108" max="16108" width="29.26953125" style="1" customWidth="1"/>
+    <col min="16109" max="16110" width="28.7265625" style="1" customWidth="1"/>
+    <col min="16111" max="16113" width="9.1796875" style="1"/>
+    <col min="16114" max="16114" width="36.81640625" style="1" customWidth="1"/>
+    <col min="16115" max="16115" width="31.26953125" style="1" customWidth="1"/>
+    <col min="16116" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25"/>
     </row>
-    <row r="2" spans="1:6" ht="39.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:6" ht="40" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
     </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2793,232 +2808,251 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>40</v>
+      <c r="B6" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="38" t="s">
+        <v>36</v>
+      </c>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="30"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="D7" s="39"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="25" t="s">
-        <v>35</v>
+      <c r="F7" s="34" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="12"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="14"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="26"/>
+      <c r="F8" s="35"/>
     </row>
-    <row r="9" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="27"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="36"/>
     </row>
-    <row r="10" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="25" t="s">
-        <v>34</v>
+      <c r="C10" s="36"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="34" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="27"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="13"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
     </row>
-    <row r="12" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="14"/>
       <c r="D12" s="13"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="27"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="36"/>
     </row>
-    <row r="13" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="12"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="12"/>
-      <c r="E13" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="18"/>
+      <c r="E13" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:6" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="26"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="18"/>
+      <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="27"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="13"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="17"/>
+      <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="18"/>
+      <c r="B17" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="18"/>
+      <c r="B19" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="18"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="16"/>
     </row>
-    <row r="21" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="20"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="17"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+    <row r="22" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="24"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B4:B5"/>
@@ -3026,20 +3060,6 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="C19:C21"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="58" fitToWidth="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
